--- a/Demo/MDA/demo_mda_9999_3_med_treatment.xlsx
+++ b/Demo/MDA/demo_mda_9999_3_med_treatment.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yumbad\Repositories\dsa-forms\Demo\MDA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5F33A04-5D7E-4473-8C66-9484DD54D93F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E87317F-A2F2-4B86-B859-1077D71D2061}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44,7 +44,7 @@
     <author>tc={E5C8D677-FE59-4CB7-A7BE-A8304FAE7637}</author>
   </authors>
   <commentList>
-    <comment ref="H93" authorId="0" shapeId="0" xr:uid="{85BEB17F-083C-4DC7-BF7F-384204A6E38C}">
+    <comment ref="H94" authorId="0" shapeId="0" xr:uid="{85BEB17F-083C-4DC7-BF7F-384204A6E38C}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -52,7 +52,7 @@
     Should be changed to AZM.TAB</t>
       </text>
     </comment>
-    <comment ref="H97" authorId="1" shapeId="0" xr:uid="{3FE006F7-E9BA-4E28-8890-9A34D71DA23D}">
+    <comment ref="H98" authorId="1" shapeId="0" xr:uid="{3FE006F7-E9BA-4E28-8890-9A34D71DA23D}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -60,7 +60,7 @@
     Should be changed to AZM.TAB</t>
       </text>
     </comment>
-    <comment ref="H102" authorId="2" shapeId="0" xr:uid="{654CB07C-43FB-4011-AE56-E1227BE30651}">
+    <comment ref="H103" authorId="2" shapeId="0" xr:uid="{654CB07C-43FB-4011-AE56-E1227BE30651}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -68,7 +68,7 @@
     The group will change to AZM.SUP</t>
       </text>
     </comment>
-    <comment ref="H107" authorId="3" shapeId="0" xr:uid="{E1842036-A1FE-4222-AB81-DC1A8A32D2BF}">
+    <comment ref="H108" authorId="3" shapeId="0" xr:uid="{E1842036-A1FE-4222-AB81-DC1A8A32D2BF}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -76,7 +76,7 @@
     The group will change to AZM.SUP</t>
       </text>
     </comment>
-    <comment ref="C116" authorId="4" shapeId="0" xr:uid="{E5C8D677-FE59-4CB7-A7BE-A8304FAE7637}">
+    <comment ref="C117" authorId="4" shapeId="0" xr:uid="{E5C8D677-FE59-4CB7-A7BE-A8304FAE7637}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -89,7 +89,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="632" uniqueCount="283">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="639" uniqueCount="288">
   <si>
     <t>type</t>
   </si>
@@ -769,9 +769,6 @@
     <t>p_medicine</t>
   </si>
   <si>
-    <t>You cannot select a single medicine together with its combination version</t>
-  </si>
-  <si>
     <t xml:space="preserve">selected(${p_medicine}, 'IVM+ALB+DEC') </t>
   </si>
   <si>
@@ -892,57 +889,6 @@
     <t>Disease covered by the TDM?</t>
   </si>
   <si>
-    <t>not(
-  selected(${p_disease}, 'LF') and
-  selected(${p_disease}, 'ONCHO') and
-  selected(${p_medicine}, 'IVM')
-)
-and
-not(
-  selected(${p_disease}, 'STH') and
-  selected(${p_disease}, 'SCHISTO') and
-  (
-    selected(${p_medicine}, 'ALB') or
-    selected(${p_medicine}, 'MEB') or
-    selected(${p_medicine}, 'PZQ')
-  )
-)
-and
-not(
-  selected(${p_disease}, 'SCHISTO') and
-  not(selected(${p_disease}, 'STH')) and
-  (
-    selected(${p_medicine}, 'PZQ+ALB') or
-    selected(${p_medicine}, 'PZQ+MEB')
-  )
-)
-and
-not(selected(${p_medicine}, 'IVM') and not(selected(${p_disease}, 'ONCHO') and not(selected(${p_disease}, 'LF'))))
-and
-not(selected(${p_medicine}, 'IVM+ALB') and not(selected(${p_disease}, 'LF') or selected(${p_disease}, 'ONCHO')))
-and
-not(selected(${p_medicine}, 'IVM+ALB+DEC') and not(selected(${p_disease}, 'LF')))
-and
-not(selected(${p_medicine}, 'ALB') and not(selected(${p_disease}, 'STH')))
-and
-not(selected(${p_medicine}, 'MEB') and not(selected(${p_disease}, 'STH')))
-and
-not(selected(${p_medicine}, 'PZQ') and not(selected(${p_disease}, 'SCHISTO')))
-and
-not(selected(${p_medicine}, 'PZQ+ALB') and not(selected(${p_disease}, 'SCHISTO') or selected(${p_disease}, 'STH')))
-and
-not(selected(${p_medicine}, 'PZQ+MEB') and not(selected(${p_disease}, 'SCHISTO') or selected(${p_disease}, 'STH')))
-and
-not(selected(${p_medicine}, 'AZM.TAB') and not(selected(${p_disease}, 'TRACHOMA')))
-and
-not(selected(${p_medicine}, 'AZM.SUSP') and not(selected(${p_disease}, 'TRACHOMA')))
-and
-not(selected(${p_medicine}, 'TETRA') and not(selected(${p_disease}, 'TRACHOMA')))</t>
-  </si>
-  <si>
-    <t>selected(${p_disease}, disease_filter)</t>
-  </si>
-  <si>
     <t>disease_filter</t>
   </si>
   <si>
@@ -983,6 +929,30 @@
   </si>
   <si>
     <t>tetra_reason_not_treated</t>
+  </si>
+  <si>
+    <t>p_health_facility</t>
+  </si>
+  <si>
+    <t>Select the Health facility / Sub district</t>
+  </si>
+  <si>
+    <t>col_5</t>
+  </si>
+  <si>
+    <t>${p_state}</t>
+  </si>
+  <si>
+    <t>${p_district}</t>
+  </si>
+  <si>
+    <t>${p_health_facility}</t>
+  </si>
+  <si>
+    <t>${p_location}</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> selected(${p_disease}, disease_filter)</t>
   </si>
 </sst>
 </file>
@@ -1474,19 +1444,19 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="H93" dT="2026-04-01T12:17:34.10" personId="{C8E238ED-59BE-4071-A008-C5EB07D4B2F5}" id="{85BEB17F-083C-4DC7-BF7F-384204A6E38C}">
+  <threadedComment ref="H94" dT="2026-04-01T12:17:34.10" personId="{C8E238ED-59BE-4071-A008-C5EB07D4B2F5}" id="{85BEB17F-083C-4DC7-BF7F-384204A6E38C}">
     <text>Should be changed to AZM.TAB</text>
   </threadedComment>
-  <threadedComment ref="H97" dT="2026-04-01T12:17:34.10" personId="{C8E238ED-59BE-4071-A008-C5EB07D4B2F5}" id="{3FE006F7-E9BA-4E28-8890-9A34D71DA23D}">
+  <threadedComment ref="H98" dT="2026-04-01T12:17:34.10" personId="{C8E238ED-59BE-4071-A008-C5EB07D4B2F5}" id="{3FE006F7-E9BA-4E28-8890-9A34D71DA23D}">
     <text>Should be changed to AZM.TAB</text>
   </threadedComment>
-  <threadedComment ref="H102" dT="2026-04-01T11:41:32.32" personId="{C8E238ED-59BE-4071-A008-C5EB07D4B2F5}" id="{654CB07C-43FB-4011-AE56-E1227BE30651}">
+  <threadedComment ref="H103" dT="2026-04-01T11:41:32.32" personId="{C8E238ED-59BE-4071-A008-C5EB07D4B2F5}" id="{654CB07C-43FB-4011-AE56-E1227BE30651}">
     <text>The group will change to AZM.SUP</text>
   </threadedComment>
-  <threadedComment ref="H107" dT="2026-04-01T11:41:32.32" personId="{C8E238ED-59BE-4071-A008-C5EB07D4B2F5}" id="{E1842036-A1FE-4222-AB81-DC1A8A32D2BF}">
+  <threadedComment ref="H108" dT="2026-04-01T11:41:32.32" personId="{C8E238ED-59BE-4071-A008-C5EB07D4B2F5}" id="{E1842036-A1FE-4222-AB81-DC1A8A32D2BF}">
     <text>The group will change to AZM.SUP</text>
   </threadedComment>
-  <threadedComment ref="C116" dT="2026-04-01T12:17:54.63" personId="{C8E238ED-59BE-4071-A008-C5EB07D4B2F5}" id="{E5C8D677-FE59-4CB7-A7BE-A8304FAE7637}">
+  <threadedComment ref="C117" dT="2026-04-01T12:17:54.63" personId="{C8E238ED-59BE-4071-A008-C5EB07D4B2F5}" id="{E5C8D677-FE59-4CB7-A7BE-A8304FAE7637}">
     <text>Change to pregnant women</text>
   </threadedComment>
 </ThreadedComments>
@@ -1494,7 +1464,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U133"/>
+  <dimension ref="A1:U134"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="24.25" style="4" bestFit="1" customWidth="1"/>
@@ -1667,7 +1637,9 @@
       <c r="P4" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="Q4" s="8"/>
+      <c r="Q4" s="8" t="s">
+        <v>283</v>
+      </c>
       <c r="R4" s="8"/>
       <c r="S4" s="8"/>
       <c r="T4" s="8"/>
@@ -1678,10 +1650,10 @@
         <v>15</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>47</v>
+        <v>280</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>43</v>
+        <v>281</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="8"/>
@@ -1701,7 +1673,9 @@
         <v>38</v>
       </c>
       <c r="Q5" s="8"/>
-      <c r="R5" s="8"/>
+      <c r="R5" s="8" t="s">
+        <v>284</v>
+      </c>
       <c r="S5" s="8"/>
       <c r="T5" s="8"/>
       <c r="U5" s="8"/>
@@ -1711,10 +1685,10 @@
         <v>15</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D6" s="9"/>
       <c r="E6" s="8"/>
@@ -1735,19 +1709,21 @@
       </c>
       <c r="Q6" s="8"/>
       <c r="R6" s="8"/>
-      <c r="S6" s="8"/>
+      <c r="S6" s="8" t="s">
+        <v>285</v>
+      </c>
       <c r="T6" s="8"/>
       <c r="U6" s="8"/>
     </row>
     <row r="7" spans="1:21">
       <c r="A7" s="8" t="s">
-        <v>64</v>
+        <v>15</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="D7" s="9"/>
       <c r="E7" s="8"/>
@@ -1763,24 +1739,36 @@
       <c r="M7" s="8"/>
       <c r="N7" s="8"/>
       <c r="O7" s="8"/>
-      <c r="P7" s="8"/>
+      <c r="P7" s="17" t="s">
+        <v>282</v>
+      </c>
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
       <c r="S7" s="8"/>
-      <c r="T7" s="8"/>
+      <c r="T7" s="8" t="s">
+        <v>286</v>
+      </c>
       <c r="U7" s="8"/>
     </row>
     <row r="8" spans="1:21">
-      <c r="A8" s="8"/>
-      <c r="B8" s="8"/>
-      <c r="C8" s="9"/>
+      <c r="A8" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>52</v>
+      </c>
       <c r="D8" s="9"/>
       <c r="E8" s="8"/>
-      <c r="F8" s="18"/>
+      <c r="F8" s="8"/>
       <c r="G8" s="9"/>
       <c r="H8" s="8"/>
       <c r="I8" s="8"/>
-      <c r="J8" s="7"/>
+      <c r="J8" s="7" t="s">
+        <v>14</v>
+      </c>
       <c r="K8" s="8"/>
       <c r="L8" s="8"/>
       <c r="M8" s="8"/>
@@ -1794,64 +1782,50 @@
       <c r="U8" s="8"/>
     </row>
     <row r="9" spans="1:21">
-      <c r="A9" s="8" t="s">
-        <v>223</v>
-      </c>
-      <c r="B9" s="8" t="s">
-        <v>224</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>266</v>
-      </c>
+      <c r="A9" s="8"/>
+      <c r="B9" s="8"/>
+      <c r="C9" s="9"/>
       <c r="D9" s="9"/>
       <c r="E9" s="8"/>
-      <c r="F9" s="8"/>
+      <c r="F9" s="18"/>
       <c r="G9" s="9"/>
       <c r="H9" s="8"/>
       <c r="I9" s="8"/>
-      <c r="J9" s="7" t="s">
-        <v>14</v>
-      </c>
+      <c r="J9" s="7"/>
       <c r="K9" s="8"/>
       <c r="L9" s="8"/>
       <c r="M9" s="8"/>
       <c r="N9" s="8"/>
       <c r="O9" s="8"/>
-      <c r="P9" s="17"/>
+      <c r="P9" s="8"/>
       <c r="Q9" s="8"/>
       <c r="R9" s="8"/>
       <c r="S9" s="8"/>
       <c r="T9" s="8"/>
       <c r="U9" s="8"/>
     </row>
-    <row r="10" spans="1:21" ht="409.5">
+    <row r="10" spans="1:21">
       <c r="A10" s="8" t="s">
-        <v>80</v>
+        <v>223</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C10" s="9" t="s">
         <v>265</v>
       </c>
       <c r="D10" s="9"/>
       <c r="E10" s="8"/>
-      <c r="F10" s="18" t="s">
-        <v>267</v>
-      </c>
-      <c r="G10" s="9" t="s">
-        <v>226</v>
-      </c>
+      <c r="F10" s="8"/>
+      <c r="G10" s="9"/>
       <c r="H10" s="8"/>
       <c r="I10" s="8"/>
-      <c r="J10" s="13" t="s">
+      <c r="J10" s="7" t="s">
         <v>14</v>
       </c>
       <c r="K10" s="8"/>
       <c r="L10" s="8"/>
-      <c r="M10" s="31" t="s">
-        <v>268</v>
-      </c>
+      <c r="M10" s="8"/>
       <c r="N10" s="8"/>
       <c r="O10" s="8"/>
       <c r="P10" s="17"/>
@@ -1862,22 +1836,32 @@
       <c r="U10" s="8"/>
     </row>
     <row r="11" spans="1:21">
-      <c r="A11" s="8"/>
-      <c r="B11" s="8"/>
-      <c r="C11" s="9"/>
+      <c r="A11" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>225</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>264</v>
+      </c>
       <c r="D11" s="9"/>
       <c r="E11" s="8"/>
-      <c r="F11" s="8"/>
+      <c r="F11" s="18"/>
       <c r="G11" s="9"/>
       <c r="H11" s="8"/>
       <c r="I11" s="8"/>
-      <c r="J11" s="7"/>
+      <c r="J11" s="13" t="s">
+        <v>14</v>
+      </c>
       <c r="K11" s="8"/>
       <c r="L11" s="8"/>
-      <c r="M11" s="8"/>
+      <c r="M11" s="31" t="s">
+        <v>287</v>
+      </c>
       <c r="N11" s="8"/>
       <c r="O11" s="8"/>
-      <c r="P11" s="8"/>
+      <c r="P11" s="17"/>
       <c r="Q11" s="8"/>
       <c r="R11" s="8"/>
       <c r="S11" s="8"/>
@@ -1885,74 +1869,66 @@
       <c r="U11" s="8"/>
     </row>
     <row r="12" spans="1:21">
-      <c r="A12" s="19" t="s">
+      <c r="A12" s="8"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="9"/>
+      <c r="D12" s="9"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8"/>
+      <c r="G12" s="9"/>
+      <c r="H12" s="8"/>
+      <c r="I12" s="8"/>
+      <c r="J12" s="7"/>
+      <c r="K12" s="8"/>
+      <c r="L12" s="8"/>
+      <c r="M12" s="8"/>
+      <c r="N12" s="8"/>
+      <c r="O12" s="8"/>
+      <c r="P12" s="8"/>
+      <c r="Q12" s="8"/>
+      <c r="R12" s="8"/>
+      <c r="S12" s="8"/>
+      <c r="T12" s="8"/>
+      <c r="U12" s="8"/>
+    </row>
+    <row r="13" spans="1:21">
+      <c r="A13" s="19" t="s">
         <v>66</v>
       </c>
-      <c r="B12" s="19" t="s">
+      <c r="B13" s="19" t="s">
         <v>177</v>
       </c>
-      <c r="C12" s="19" t="s">
+      <c r="C13" s="19" t="s">
         <v>178</v>
       </c>
-      <c r="D12" s="19"/>
-      <c r="E12" s="19"/>
-      <c r="F12" s="19"/>
-      <c r="G12" s="19"/>
-      <c r="H12" s="19"/>
-      <c r="I12" s="19"/>
-      <c r="J12" s="20"/>
-      <c r="K12" s="19"/>
-      <c r="L12" s="19"/>
-      <c r="M12" s="19"/>
-      <c r="N12" s="19"/>
-      <c r="O12" s="19"/>
-      <c r="P12" s="19"/>
-      <c r="Q12" s="19"/>
-      <c r="R12" s="19"/>
-      <c r="S12" s="19"/>
-      <c r="T12" s="19"/>
-      <c r="U12" s="19"/>
-    </row>
-    <row r="13" spans="1:21">
-      <c r="A13" s="8" t="s">
-        <v>254</v>
-      </c>
-      <c r="B13" s="8" t="s">
-        <v>250</v>
-      </c>
-      <c r="C13" s="9" t="s">
-        <v>251</v>
-      </c>
-      <c r="D13" s="9"/>
-      <c r="E13" s="8"/>
-      <c r="F13" s="8"/>
-      <c r="G13" s="9"/>
-      <c r="H13" s="8"/>
-      <c r="I13" s="8"/>
-      <c r="J13" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="K13" s="8"/>
-      <c r="L13" s="8"/>
-      <c r="M13" s="8"/>
-      <c r="N13" s="8"/>
-      <c r="O13" s="8"/>
-      <c r="P13" s="8"/>
-      <c r="Q13" s="8"/>
-      <c r="R13" s="8"/>
-      <c r="S13" s="8"/>
-      <c r="T13" s="8"/>
-      <c r="U13" s="8"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="19"/>
+      <c r="G13" s="19"/>
+      <c r="H13" s="19"/>
+      <c r="I13" s="19"/>
+      <c r="J13" s="20"/>
+      <c r="K13" s="19"/>
+      <c r="L13" s="19"/>
+      <c r="M13" s="19"/>
+      <c r="N13" s="19"/>
+      <c r="O13" s="19"/>
+      <c r="P13" s="19"/>
+      <c r="Q13" s="19"/>
+      <c r="R13" s="19"/>
+      <c r="S13" s="19"/>
+      <c r="T13" s="19"/>
+      <c r="U13" s="19"/>
     </row>
     <row r="14" spans="1:21">
       <c r="A14" s="8" t="s">
-        <v>13</v>
+        <v>253</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>171</v>
+        <v>249</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>172</v>
+        <v>250</v>
       </c>
       <c r="D14" s="9"/>
       <c r="E14" s="8"/>
@@ -1960,7 +1936,9 @@
       <c r="G14" s="9"/>
       <c r="H14" s="8"/>
       <c r="I14" s="8"/>
-      <c r="J14" s="7"/>
+      <c r="J14" s="7" t="s">
+        <v>23</v>
+      </c>
       <c r="K14" s="8"/>
       <c r="L14" s="8"/>
       <c r="M14" s="8"/>
@@ -1978,10 +1956,10 @@
         <v>13</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D15" s="9"/>
       <c r="E15" s="8"/>
@@ -2007,10 +1985,10 @@
         <v>13</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D16" s="9"/>
       <c r="E16" s="8"/>
@@ -2033,10 +2011,14 @@
     </row>
     <row r="17" spans="1:21">
       <c r="A17" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="B17" s="8"/>
-      <c r="C17" s="9"/>
+        <v>13</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>176</v>
+      </c>
       <c r="D17" s="9"/>
       <c r="E17" s="8"/>
       <c r="F17" s="8"/>
@@ -2057,76 +2039,70 @@
       <c r="U17" s="8"/>
     </row>
     <row r="18" spans="1:21">
-      <c r="A18" s="19" t="s">
+      <c r="A18" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="B18" s="8"/>
+      <c r="C18" s="9"/>
+      <c r="D18" s="9"/>
+      <c r="E18" s="8"/>
+      <c r="F18" s="8"/>
+      <c r="G18" s="9"/>
+      <c r="H18" s="8"/>
+      <c r="I18" s="8"/>
+      <c r="J18" s="7"/>
+      <c r="K18" s="8"/>
+      <c r="L18" s="8"/>
+      <c r="M18" s="8"/>
+      <c r="N18" s="8"/>
+      <c r="O18" s="8"/>
+      <c r="P18" s="8"/>
+      <c r="Q18" s="8"/>
+      <c r="R18" s="8"/>
+      <c r="S18" s="8"/>
+      <c r="T18" s="8"/>
+      <c r="U18" s="8"/>
+    </row>
+    <row r="19" spans="1:21">
+      <c r="A19" s="19" t="s">
         <v>66</v>
       </c>
-      <c r="B18" s="19" t="s">
+      <c r="B19" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="C18" s="19" t="s">
+      <c r="C19" s="19" t="s">
         <v>96</v>
       </c>
-      <c r="D18" s="19"/>
-      <c r="E18" s="19"/>
-      <c r="F18" s="19"/>
-      <c r="G18" s="19"/>
-      <c r="H18" s="19" t="s">
-        <v>227</v>
-      </c>
-      <c r="I18" s="19"/>
-      <c r="J18" s="20"/>
-      <c r="K18" s="19"/>
-      <c r="L18" s="19"/>
-      <c r="M18" s="19"/>
-      <c r="N18" s="19"/>
-      <c r="O18" s="19"/>
-      <c r="P18" s="19"/>
-      <c r="Q18" s="19"/>
-      <c r="R18" s="19"/>
-      <c r="S18" s="19"/>
-      <c r="T18" s="19"/>
-      <c r="U18" s="19"/>
-    </row>
-    <row r="19" spans="1:21">
-      <c r="A19" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="B19" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="C19" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="D19" s="9"/>
-      <c r="E19" s="8"/>
-      <c r="F19" s="8"/>
-      <c r="G19" s="9"/>
-      <c r="H19" s="8"/>
-      <c r="I19" s="8"/>
-      <c r="J19" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="K19" s="8"/>
-      <c r="L19" s="8"/>
-      <c r="M19" s="8"/>
-      <c r="N19" s="8"/>
-      <c r="O19" s="8"/>
-      <c r="P19" s="8"/>
-      <c r="Q19" s="8"/>
-      <c r="R19" s="8"/>
-      <c r="S19" s="8"/>
-      <c r="T19" s="8"/>
-      <c r="U19" s="8"/>
+      <c r="D19" s="19"/>
+      <c r="E19" s="19"/>
+      <c r="F19" s="19"/>
+      <c r="G19" s="19"/>
+      <c r="H19" s="19" t="s">
+        <v>226</v>
+      </c>
+      <c r="I19" s="19"/>
+      <c r="J19" s="20"/>
+      <c r="K19" s="19"/>
+      <c r="L19" s="19"/>
+      <c r="M19" s="19"/>
+      <c r="N19" s="19"/>
+      <c r="O19" s="19"/>
+      <c r="P19" s="19"/>
+      <c r="Q19" s="19"/>
+      <c r="R19" s="19"/>
+      <c r="S19" s="19"/>
+      <c r="T19" s="19"/>
+      <c r="U19" s="19"/>
     </row>
     <row r="20" spans="1:21">
       <c r="A20" s="8" t="s">
         <v>13</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D20" s="9"/>
       <c r="E20" s="8"/>
@@ -2154,10 +2130,10 @@
         <v>13</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D21" s="9"/>
       <c r="E21" s="8"/>
@@ -2185,10 +2161,10 @@
         <v>13</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D22" s="9"/>
       <c r="E22" s="8"/>
@@ -2211,25 +2187,25 @@
       <c r="T22" s="8"/>
       <c r="U22" s="8"/>
     </row>
-    <row r="23" spans="1:21" ht="31.5">
+    <row r="23" spans="1:21">
       <c r="A23" s="8" t="s">
-        <v>78</v>
+        <v>13</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="D23" s="9"/>
       <c r="E23" s="8"/>
       <c r="F23" s="8"/>
       <c r="G23" s="9"/>
       <c r="H23" s="8"/>
-      <c r="I23" s="18" t="s">
-        <v>88</v>
-      </c>
-      <c r="J23" s="7"/>
+      <c r="I23" s="8"/>
+      <c r="J23" s="7" t="s">
+        <v>14</v>
+      </c>
       <c r="K23" s="8"/>
       <c r="L23" s="8"/>
       <c r="M23" s="8"/>
@@ -2247,10 +2223,10 @@
         <v>78</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D24" s="9"/>
       <c r="E24" s="8"/>
@@ -2258,7 +2234,7 @@
       <c r="G24" s="9"/>
       <c r="H24" s="8"/>
       <c r="I24" s="18" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="J24" s="7"/>
       <c r="K24" s="8"/>
@@ -2273,18 +2249,24 @@
       <c r="T24" s="8"/>
       <c r="U24" s="8"/>
     </row>
-    <row r="25" spans="1:21">
-      <c r="A25" s="21" t="s">
-        <v>79</v>
-      </c>
-      <c r="B25" s="8"/>
-      <c r="C25" s="9"/>
+    <row r="25" spans="1:21" ht="31.5">
+      <c r="A25" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="B25" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>68</v>
+      </c>
       <c r="D25" s="9"/>
       <c r="E25" s="8"/>
       <c r="F25" s="8"/>
       <c r="G25" s="9"/>
       <c r="H25" s="8"/>
-      <c r="I25" s="8"/>
+      <c r="I25" s="18" t="s">
+        <v>90</v>
+      </c>
       <c r="J25" s="7"/>
       <c r="K25" s="8"/>
       <c r="L25" s="8"/>
@@ -2298,77 +2280,71 @@
       <c r="T25" s="8"/>
       <c r="U25" s="8"/>
     </row>
-    <row r="26" spans="1:21" s="28" customFormat="1">
-      <c r="A26" s="29" t="s">
+    <row r="26" spans="1:21">
+      <c r="A26" s="21" t="s">
+        <v>79</v>
+      </c>
+      <c r="B26" s="8"/>
+      <c r="C26" s="9"/>
+      <c r="D26" s="9"/>
+      <c r="E26" s="8"/>
+      <c r="F26" s="8"/>
+      <c r="G26" s="9"/>
+      <c r="H26" s="8"/>
+      <c r="I26" s="8"/>
+      <c r="J26" s="7"/>
+      <c r="K26" s="8"/>
+      <c r="L26" s="8"/>
+      <c r="M26" s="8"/>
+      <c r="N26" s="8"/>
+      <c r="O26" s="8"/>
+      <c r="P26" s="8"/>
+      <c r="Q26" s="8"/>
+      <c r="R26" s="8"/>
+      <c r="S26" s="8"/>
+      <c r="T26" s="8"/>
+      <c r="U26" s="8"/>
+    </row>
+    <row r="27" spans="1:21" s="28" customFormat="1">
+      <c r="A27" s="29" t="s">
         <v>66</v>
       </c>
-      <c r="B26" s="29" t="s">
-        <v>276</v>
-      </c>
-      <c r="C26" s="29" t="s">
-        <v>259</v>
-      </c>
-      <c r="D26" s="29"/>
-      <c r="E26" s="29"/>
-      <c r="F26" s="29"/>
-      <c r="G26" s="29"/>
-      <c r="H26" s="29" t="s">
-        <v>227</v>
-      </c>
-      <c r="I26" s="29"/>
-      <c r="J26" s="30"/>
-      <c r="K26" s="29"/>
-      <c r="L26" s="29"/>
-      <c r="M26" s="29"/>
-      <c r="N26" s="29"/>
-      <c r="O26" s="29"/>
-      <c r="P26" s="29"/>
-      <c r="Q26" s="29"/>
-      <c r="R26" s="29"/>
-      <c r="S26" s="29"/>
-      <c r="T26" s="29"/>
-      <c r="U26" s="29"/>
-    </row>
-    <row r="27" spans="1:21">
-      <c r="A27" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="B27" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="C27" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="D27" s="9"/>
-      <c r="E27" s="8"/>
-      <c r="F27" s="8"/>
-      <c r="G27" s="9"/>
-      <c r="H27" s="8"/>
-      <c r="I27" s="8"/>
-      <c r="J27" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="K27" s="8"/>
-      <c r="L27" s="8"/>
-      <c r="M27" s="8"/>
-      <c r="N27" s="8"/>
-      <c r="O27" s="8"/>
-      <c r="P27" s="8"/>
-      <c r="Q27" s="8"/>
-      <c r="R27" s="8"/>
-      <c r="S27" s="8"/>
-      <c r="T27" s="8"/>
-      <c r="U27" s="8"/>
+      <c r="B27" s="29" t="s">
+        <v>273</v>
+      </c>
+      <c r="C27" s="29" t="s">
+        <v>258</v>
+      </c>
+      <c r="D27" s="29"/>
+      <c r="E27" s="29"/>
+      <c r="F27" s="29"/>
+      <c r="G27" s="29"/>
+      <c r="H27" s="29" t="s">
+        <v>226</v>
+      </c>
+      <c r="I27" s="29"/>
+      <c r="J27" s="30"/>
+      <c r="K27" s="29"/>
+      <c r="L27" s="29"/>
+      <c r="M27" s="29"/>
+      <c r="N27" s="29"/>
+      <c r="O27" s="29"/>
+      <c r="P27" s="29"/>
+      <c r="Q27" s="29"/>
+      <c r="R27" s="29"/>
+      <c r="S27" s="29"/>
+      <c r="T27" s="29"/>
+      <c r="U27" s="29"/>
     </row>
     <row r="28" spans="1:21">
       <c r="A28" s="8" t="s">
         <v>13</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D28" s="9"/>
       <c r="E28" s="8"/>
@@ -2396,10 +2372,10 @@
         <v>13</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D29" s="9"/>
       <c r="E29" s="8"/>
@@ -2427,10 +2403,10 @@
         <v>13</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D30" s="9"/>
       <c r="E30" s="8"/>
@@ -2458,10 +2434,10 @@
         <v>13</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D31" s="9"/>
       <c r="E31" s="8"/>
@@ -2485,18 +2461,24 @@
       <c r="U31" s="8"/>
     </row>
     <row r="32" spans="1:21">
-      <c r="A32" s="21" t="s">
-        <v>79</v>
-      </c>
-      <c r="B32" s="8"/>
-      <c r="C32" s="9"/>
+      <c r="A32" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B32" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="C32" s="9" t="s">
+        <v>73</v>
+      </c>
       <c r="D32" s="9"/>
       <c r="E32" s="8"/>
       <c r="F32" s="8"/>
       <c r="G32" s="9"/>
       <c r="H32" s="8"/>
       <c r="I32" s="8"/>
-      <c r="J32" s="7"/>
+      <c r="J32" s="7" t="s">
+        <v>14</v>
+      </c>
       <c r="K32" s="8"/>
       <c r="L32" s="8"/>
       <c r="M32" s="8"/>
@@ -2510,76 +2492,70 @@
       <c r="U32" s="8"/>
     </row>
     <row r="33" spans="1:21">
-      <c r="A33" s="19" t="s">
+      <c r="A33" s="21" t="s">
+        <v>79</v>
+      </c>
+      <c r="B33" s="8"/>
+      <c r="C33" s="9"/>
+      <c r="D33" s="9"/>
+      <c r="E33" s="8"/>
+      <c r="F33" s="8"/>
+      <c r="G33" s="9"/>
+      <c r="H33" s="8"/>
+      <c r="I33" s="8"/>
+      <c r="J33" s="7"/>
+      <c r="K33" s="8"/>
+      <c r="L33" s="8"/>
+      <c r="M33" s="8"/>
+      <c r="N33" s="8"/>
+      <c r="O33" s="8"/>
+      <c r="P33" s="8"/>
+      <c r="Q33" s="8"/>
+      <c r="R33" s="8"/>
+      <c r="S33" s="8"/>
+      <c r="T33" s="8"/>
+      <c r="U33" s="8"/>
+    </row>
+    <row r="34" spans="1:21">
+      <c r="A34" s="19" t="s">
         <v>66</v>
       </c>
-      <c r="B33" s="19" t="s">
+      <c r="B34" s="19" t="s">
         <v>180</v>
       </c>
-      <c r="C33" s="19" t="s">
+      <c r="C34" s="19" t="s">
         <v>194</v>
       </c>
-      <c r="D33" s="19"/>
-      <c r="E33" s="19"/>
-      <c r="F33" s="19"/>
-      <c r="G33" s="19"/>
-      <c r="H33" s="19" t="s">
-        <v>257</v>
-      </c>
-      <c r="I33" s="19"/>
-      <c r="J33" s="20"/>
-      <c r="K33" s="19"/>
-      <c r="L33" s="19"/>
-      <c r="M33" s="19"/>
-      <c r="N33" s="19"/>
-      <c r="O33" s="19"/>
-      <c r="P33" s="19"/>
-      <c r="Q33" s="19"/>
-      <c r="R33" s="19"/>
-      <c r="S33" s="19"/>
-      <c r="T33" s="19"/>
-      <c r="U33" s="19"/>
-    </row>
-    <row r="34" spans="1:21">
-      <c r="A34" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="B34" s="8" t="s">
-        <v>181</v>
-      </c>
-      <c r="C34" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="D34" s="9"/>
-      <c r="E34" s="8"/>
-      <c r="F34" s="8"/>
-      <c r="G34" s="9"/>
-      <c r="H34" s="8"/>
-      <c r="I34" s="8"/>
-      <c r="J34" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="K34" s="8"/>
-      <c r="L34" s="8"/>
-      <c r="M34" s="8"/>
-      <c r="N34" s="8"/>
-      <c r="O34" s="8"/>
-      <c r="P34" s="8"/>
-      <c r="Q34" s="8"/>
-      <c r="R34" s="8"/>
-      <c r="S34" s="8"/>
-      <c r="T34" s="8"/>
-      <c r="U34" s="8"/>
+      <c r="D34" s="19"/>
+      <c r="E34" s="19"/>
+      <c r="F34" s="19"/>
+      <c r="G34" s="19"/>
+      <c r="H34" s="19" t="s">
+        <v>256</v>
+      </c>
+      <c r="I34" s="19"/>
+      <c r="J34" s="20"/>
+      <c r="K34" s="19"/>
+      <c r="L34" s="19"/>
+      <c r="M34" s="19"/>
+      <c r="N34" s="19"/>
+      <c r="O34" s="19"/>
+      <c r="P34" s="19"/>
+      <c r="Q34" s="19"/>
+      <c r="R34" s="19"/>
+      <c r="S34" s="19"/>
+      <c r="T34" s="19"/>
+      <c r="U34" s="19"/>
     </row>
     <row r="35" spans="1:21">
       <c r="A35" s="8" t="s">
         <v>13</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C35" s="9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D35" s="9"/>
       <c r="E35" s="8"/>
@@ -2607,10 +2583,10 @@
         <v>13</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D36" s="9"/>
       <c r="E36" s="8"/>
@@ -2638,10 +2614,10 @@
         <v>13</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D37" s="9"/>
       <c r="E37" s="8"/>
@@ -2664,25 +2640,25 @@
       <c r="T37" s="8"/>
       <c r="U37" s="8"/>
     </row>
-    <row r="38" spans="1:21" ht="31.5">
+    <row r="38" spans="1:21">
       <c r="A38" s="8" t="s">
-        <v>78</v>
+        <v>13</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C38" s="9" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="D38" s="9"/>
       <c r="E38" s="8"/>
       <c r="F38" s="8"/>
       <c r="G38" s="9"/>
       <c r="H38" s="8"/>
-      <c r="I38" s="18" t="s">
-        <v>186</v>
-      </c>
-      <c r="J38" s="7"/>
+      <c r="I38" s="8"/>
+      <c r="J38" s="7" t="s">
+        <v>14</v>
+      </c>
       <c r="K38" s="8"/>
       <c r="L38" s="8"/>
       <c r="M38" s="8"/>
@@ -2700,10 +2676,10 @@
         <v>78</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D39" s="9"/>
       <c r="E39" s="8"/>
@@ -2711,7 +2687,7 @@
       <c r="G39" s="9"/>
       <c r="H39" s="8"/>
       <c r="I39" s="18" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="J39" s="7"/>
       <c r="K39" s="8"/>
@@ -2726,18 +2702,24 @@
       <c r="T39" s="8"/>
       <c r="U39" s="8"/>
     </row>
-    <row r="40" spans="1:21">
-      <c r="A40" s="21" t="s">
-        <v>79</v>
-      </c>
-      <c r="B40" s="8"/>
-      <c r="C40" s="9"/>
+    <row r="40" spans="1:21" ht="31.5">
+      <c r="A40" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="B40" s="8" t="s">
+        <v>187</v>
+      </c>
+      <c r="C40" s="9" t="s">
+        <v>68</v>
+      </c>
       <c r="D40" s="9"/>
       <c r="E40" s="8"/>
       <c r="F40" s="8"/>
       <c r="G40" s="9"/>
       <c r="H40" s="8"/>
-      <c r="I40" s="8"/>
+      <c r="I40" s="18" t="s">
+        <v>188</v>
+      </c>
       <c r="J40" s="7"/>
       <c r="K40" s="8"/>
       <c r="L40" s="8"/>
@@ -2751,77 +2733,71 @@
       <c r="T40" s="8"/>
       <c r="U40" s="8"/>
     </row>
-    <row r="41" spans="1:21" s="28" customFormat="1">
-      <c r="A41" s="29" t="s">
+    <row r="41" spans="1:21">
+      <c r="A41" s="21" t="s">
+        <v>79</v>
+      </c>
+      <c r="B41" s="8"/>
+      <c r="C41" s="9"/>
+      <c r="D41" s="9"/>
+      <c r="E41" s="8"/>
+      <c r="F41" s="8"/>
+      <c r="G41" s="9"/>
+      <c r="H41" s="8"/>
+      <c r="I41" s="8"/>
+      <c r="J41" s="7"/>
+      <c r="K41" s="8"/>
+      <c r="L41" s="8"/>
+      <c r="M41" s="8"/>
+      <c r="N41" s="8"/>
+      <c r="O41" s="8"/>
+      <c r="P41" s="8"/>
+      <c r="Q41" s="8"/>
+      <c r="R41" s="8"/>
+      <c r="S41" s="8"/>
+      <c r="T41" s="8"/>
+      <c r="U41" s="8"/>
+    </row>
+    <row r="42" spans="1:21" s="28" customFormat="1">
+      <c r="A42" s="29" t="s">
         <v>66</v>
       </c>
-      <c r="B41" s="29" t="s">
-        <v>275</v>
-      </c>
-      <c r="C41" s="29" t="s">
-        <v>260</v>
-      </c>
-      <c r="D41" s="29"/>
-      <c r="E41" s="29"/>
-      <c r="F41" s="29"/>
-      <c r="G41" s="29"/>
-      <c r="H41" s="29" t="s">
-        <v>257</v>
-      </c>
-      <c r="I41" s="29"/>
-      <c r="J41" s="30"/>
-      <c r="K41" s="29"/>
-      <c r="L41" s="29"/>
-      <c r="M41" s="29"/>
-      <c r="N41" s="29"/>
-      <c r="O41" s="29"/>
-      <c r="P41" s="29"/>
-      <c r="Q41" s="29"/>
-      <c r="R41" s="29"/>
-      <c r="S41" s="29"/>
-      <c r="T41" s="29"/>
-      <c r="U41" s="29"/>
-    </row>
-    <row r="42" spans="1:21">
-      <c r="A42" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="B42" s="8" t="s">
-        <v>189</v>
-      </c>
-      <c r="C42" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="D42" s="9"/>
-      <c r="E42" s="8"/>
-      <c r="F42" s="8"/>
-      <c r="G42" s="9"/>
-      <c r="H42" s="8"/>
-      <c r="I42" s="8"/>
-      <c r="J42" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="K42" s="8"/>
-      <c r="L42" s="8"/>
-      <c r="M42" s="8"/>
-      <c r="N42" s="8"/>
-      <c r="O42" s="8"/>
-      <c r="P42" s="8"/>
-      <c r="Q42" s="8"/>
-      <c r="R42" s="8"/>
-      <c r="S42" s="8"/>
-      <c r="T42" s="8"/>
-      <c r="U42" s="8"/>
+      <c r="B42" s="29" t="s">
+        <v>272</v>
+      </c>
+      <c r="C42" s="29" t="s">
+        <v>259</v>
+      </c>
+      <c r="D42" s="29"/>
+      <c r="E42" s="29"/>
+      <c r="F42" s="29"/>
+      <c r="G42" s="29"/>
+      <c r="H42" s="29" t="s">
+        <v>256</v>
+      </c>
+      <c r="I42" s="29"/>
+      <c r="J42" s="30"/>
+      <c r="K42" s="29"/>
+      <c r="L42" s="29"/>
+      <c r="M42" s="29"/>
+      <c r="N42" s="29"/>
+      <c r="O42" s="29"/>
+      <c r="P42" s="29"/>
+      <c r="Q42" s="29"/>
+      <c r="R42" s="29"/>
+      <c r="S42" s="29"/>
+      <c r="T42" s="29"/>
+      <c r="U42" s="29"/>
     </row>
     <row r="43" spans="1:21">
       <c r="A43" s="8" t="s">
         <v>13</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C43" s="9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D43" s="9"/>
       <c r="E43" s="8"/>
@@ -2849,10 +2825,10 @@
         <v>13</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C44" s="9" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D44" s="9"/>
       <c r="E44" s="8"/>
@@ -2880,10 +2856,10 @@
         <v>13</v>
       </c>
       <c r="B45" s="8" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C45" s="9" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D45" s="9"/>
       <c r="E45" s="8"/>
@@ -2911,10 +2887,10 @@
         <v>13</v>
       </c>
       <c r="B46" s="8" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C46" s="9" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D46" s="9"/>
       <c r="E46" s="8"/>
@@ -2938,18 +2914,24 @@
       <c r="U46" s="8"/>
     </row>
     <row r="47" spans="1:21">
-      <c r="A47" s="21" t="s">
-        <v>79</v>
-      </c>
-      <c r="B47" s="8"/>
-      <c r="C47" s="9"/>
+      <c r="A47" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B47" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="C47" s="9" t="s">
+        <v>73</v>
+      </c>
       <c r="D47" s="9"/>
       <c r="E47" s="8"/>
       <c r="F47" s="8"/>
       <c r="G47" s="9"/>
       <c r="H47" s="8"/>
       <c r="I47" s="8"/>
-      <c r="J47" s="7"/>
+      <c r="J47" s="7" t="s">
+        <v>14</v>
+      </c>
       <c r="K47" s="8"/>
       <c r="L47" s="8"/>
       <c r="M47" s="8"/>
@@ -2963,76 +2945,70 @@
       <c r="U47" s="8"/>
     </row>
     <row r="48" spans="1:21">
-      <c r="A48" s="19" t="s">
+      <c r="A48" s="21" t="s">
+        <v>79</v>
+      </c>
+      <c r="B48" s="8"/>
+      <c r="C48" s="9"/>
+      <c r="D48" s="9"/>
+      <c r="E48" s="8"/>
+      <c r="F48" s="8"/>
+      <c r="G48" s="9"/>
+      <c r="H48" s="8"/>
+      <c r="I48" s="8"/>
+      <c r="J48" s="7"/>
+      <c r="K48" s="8"/>
+      <c r="L48" s="8"/>
+      <c r="M48" s="8"/>
+      <c r="N48" s="8"/>
+      <c r="O48" s="8"/>
+      <c r="P48" s="8"/>
+      <c r="Q48" s="8"/>
+      <c r="R48" s="8"/>
+      <c r="S48" s="8"/>
+      <c r="T48" s="8"/>
+      <c r="U48" s="8"/>
+    </row>
+    <row r="49" spans="1:21">
+      <c r="A49" s="19" t="s">
         <v>66</v>
       </c>
-      <c r="B48" s="19" t="s">
-        <v>228</v>
-      </c>
-      <c r="C48" s="19" t="s">
+      <c r="B49" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="C49" s="19" t="s">
         <v>179</v>
       </c>
-      <c r="D48" s="19"/>
-      <c r="E48" s="19"/>
-      <c r="F48" s="19"/>
-      <c r="G48" s="19"/>
-      <c r="H48" s="19" t="s">
-        <v>255</v>
-      </c>
-      <c r="I48" s="19"/>
-      <c r="J48" s="20"/>
-      <c r="K48" s="19"/>
-      <c r="L48" s="19"/>
-      <c r="M48" s="19"/>
-      <c r="N48" s="19"/>
-      <c r="O48" s="19"/>
-      <c r="P48" s="19"/>
-      <c r="Q48" s="19"/>
-      <c r="R48" s="19"/>
-      <c r="S48" s="19"/>
-      <c r="T48" s="19"/>
-      <c r="U48" s="19"/>
-    </row>
-    <row r="49" spans="1:21">
-      <c r="A49" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="B49" s="8" t="s">
-        <v>229</v>
-      </c>
-      <c r="C49" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="D49" s="9"/>
-      <c r="E49" s="8"/>
-      <c r="F49" s="8"/>
-      <c r="G49" s="9"/>
-      <c r="H49" s="8"/>
-      <c r="I49" s="8"/>
-      <c r="J49" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="K49" s="8"/>
-      <c r="L49" s="8"/>
-      <c r="M49" s="8"/>
-      <c r="N49" s="8"/>
-      <c r="O49" s="8"/>
-      <c r="P49" s="8"/>
-      <c r="Q49" s="8"/>
-      <c r="R49" s="8"/>
-      <c r="S49" s="8"/>
-      <c r="T49" s="8"/>
-      <c r="U49" s="8"/>
+      <c r="D49" s="19"/>
+      <c r="E49" s="19"/>
+      <c r="F49" s="19"/>
+      <c r="G49" s="19"/>
+      <c r="H49" s="19" t="s">
+        <v>254</v>
+      </c>
+      <c r="I49" s="19"/>
+      <c r="J49" s="20"/>
+      <c r="K49" s="19"/>
+      <c r="L49" s="19"/>
+      <c r="M49" s="19"/>
+      <c r="N49" s="19"/>
+      <c r="O49" s="19"/>
+      <c r="P49" s="19"/>
+      <c r="Q49" s="19"/>
+      <c r="R49" s="19"/>
+      <c r="S49" s="19"/>
+      <c r="T49" s="19"/>
+      <c r="U49" s="19"/>
     </row>
     <row r="50" spans="1:21">
       <c r="A50" s="8" t="s">
         <v>13</v>
       </c>
       <c r="B50" s="8" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C50" s="9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D50" s="9"/>
       <c r="E50" s="8"/>
@@ -3060,10 +3036,10 @@
         <v>13</v>
       </c>
       <c r="B51" s="8" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C51" s="9" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D51" s="9"/>
       <c r="E51" s="8"/>
@@ -3091,10 +3067,10 @@
         <v>13</v>
       </c>
       <c r="B52" s="8" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C52" s="9" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D52" s="9"/>
       <c r="E52" s="8"/>
@@ -3117,25 +3093,25 @@
       <c r="T52" s="8"/>
       <c r="U52" s="8"/>
     </row>
-    <row r="53" spans="1:21" ht="31.5">
+    <row r="53" spans="1:21">
       <c r="A53" s="8" t="s">
-        <v>78</v>
+        <v>13</v>
       </c>
       <c r="B53" s="8" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C53" s="9" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="D53" s="9"/>
       <c r="E53" s="8"/>
       <c r="F53" s="8"/>
       <c r="G53" s="9"/>
       <c r="H53" s="8"/>
-      <c r="I53" s="18" t="s">
-        <v>234</v>
-      </c>
-      <c r="J53" s="7"/>
+      <c r="I53" s="8"/>
+      <c r="J53" s="7" t="s">
+        <v>14</v>
+      </c>
       <c r="K53" s="8"/>
       <c r="L53" s="8"/>
       <c r="M53" s="8"/>
@@ -3153,10 +3129,10 @@
         <v>78</v>
       </c>
       <c r="B54" s="8" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="C54" s="9" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D54" s="9"/>
       <c r="E54" s="8"/>
@@ -3164,7 +3140,7 @@
       <c r="G54" s="9"/>
       <c r="H54" s="8"/>
       <c r="I54" s="18" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="J54" s="7"/>
       <c r="K54" s="8"/>
@@ -3179,18 +3155,24 @@
       <c r="T54" s="8"/>
       <c r="U54" s="8"/>
     </row>
-    <row r="55" spans="1:21">
-      <c r="A55" s="21" t="s">
-        <v>79</v>
-      </c>
-      <c r="B55" s="8"/>
-      <c r="C55" s="9"/>
+    <row r="55" spans="1:21" ht="31.5">
+      <c r="A55" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="B55" s="8" t="s">
+        <v>234</v>
+      </c>
+      <c r="C55" s="9" t="s">
+        <v>68</v>
+      </c>
       <c r="D55" s="9"/>
       <c r="E55" s="8"/>
       <c r="F55" s="8"/>
       <c r="G55" s="9"/>
       <c r="H55" s="8"/>
-      <c r="I55" s="8"/>
+      <c r="I55" s="18" t="s">
+        <v>235</v>
+      </c>
       <c r="J55" s="7"/>
       <c r="K55" s="8"/>
       <c r="L55" s="8"/>
@@ -3204,77 +3186,71 @@
       <c r="T55" s="8"/>
       <c r="U55" s="8"/>
     </row>
-    <row r="56" spans="1:21" s="28" customFormat="1">
-      <c r="A56" s="29" t="s">
+    <row r="56" spans="1:21">
+      <c r="A56" s="21" t="s">
+        <v>79</v>
+      </c>
+      <c r="B56" s="8"/>
+      <c r="C56" s="9"/>
+      <c r="D56" s="9"/>
+      <c r="E56" s="8"/>
+      <c r="F56" s="8"/>
+      <c r="G56" s="9"/>
+      <c r="H56" s="8"/>
+      <c r="I56" s="8"/>
+      <c r="J56" s="7"/>
+      <c r="K56" s="8"/>
+      <c r="L56" s="8"/>
+      <c r="M56" s="8"/>
+      <c r="N56" s="8"/>
+      <c r="O56" s="8"/>
+      <c r="P56" s="8"/>
+      <c r="Q56" s="8"/>
+      <c r="R56" s="8"/>
+      <c r="S56" s="8"/>
+      <c r="T56" s="8"/>
+      <c r="U56" s="8"/>
+    </row>
+    <row r="57" spans="1:21" s="28" customFormat="1">
+      <c r="A57" s="29" t="s">
         <v>66</v>
       </c>
-      <c r="B56" s="29" t="s">
-        <v>277</v>
-      </c>
-      <c r="C56" s="29" t="s">
-        <v>261</v>
-      </c>
-      <c r="D56" s="29"/>
-      <c r="E56" s="29"/>
-      <c r="F56" s="29"/>
-      <c r="G56" s="29"/>
-      <c r="H56" s="29" t="s">
-        <v>255</v>
-      </c>
-      <c r="I56" s="29"/>
-      <c r="J56" s="30"/>
-      <c r="K56" s="29"/>
-      <c r="L56" s="29"/>
-      <c r="M56" s="29"/>
-      <c r="N56" s="29"/>
-      <c r="O56" s="29"/>
-      <c r="P56" s="29"/>
-      <c r="Q56" s="29"/>
-      <c r="R56" s="29"/>
-      <c r="S56" s="29"/>
-      <c r="T56" s="29"/>
-      <c r="U56" s="29"/>
-    </row>
-    <row r="57" spans="1:21">
-      <c r="A57" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="B57" s="8" t="s">
-        <v>237</v>
-      </c>
-      <c r="C57" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="D57" s="9"/>
-      <c r="E57" s="8"/>
-      <c r="F57" s="8"/>
-      <c r="G57" s="9"/>
-      <c r="H57" s="8"/>
-      <c r="I57" s="8"/>
-      <c r="J57" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="K57" s="8"/>
-      <c r="L57" s="8"/>
-      <c r="M57" s="8"/>
-      <c r="N57" s="8"/>
-      <c r="O57" s="8"/>
-      <c r="P57" s="8"/>
-      <c r="Q57" s="8"/>
-      <c r="R57" s="8"/>
-      <c r="S57" s="8"/>
-      <c r="T57" s="8"/>
-      <c r="U57" s="8"/>
+      <c r="B57" s="29" t="s">
+        <v>274</v>
+      </c>
+      <c r="C57" s="29" t="s">
+        <v>260</v>
+      </c>
+      <c r="D57" s="29"/>
+      <c r="E57" s="29"/>
+      <c r="F57" s="29"/>
+      <c r="G57" s="29"/>
+      <c r="H57" s="29" t="s">
+        <v>254</v>
+      </c>
+      <c r="I57" s="29"/>
+      <c r="J57" s="30"/>
+      <c r="K57" s="29"/>
+      <c r="L57" s="29"/>
+      <c r="M57" s="29"/>
+      <c r="N57" s="29"/>
+      <c r="O57" s="29"/>
+      <c r="P57" s="29"/>
+      <c r="Q57" s="29"/>
+      <c r="R57" s="29"/>
+      <c r="S57" s="29"/>
+      <c r="T57" s="29"/>
+      <c r="U57" s="29"/>
     </row>
     <row r="58" spans="1:21">
       <c r="A58" s="8" t="s">
         <v>13</v>
       </c>
       <c r="B58" s="8" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C58" s="9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D58" s="9"/>
       <c r="E58" s="8"/>
@@ -3302,10 +3278,10 @@
         <v>13</v>
       </c>
       <c r="B59" s="8" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C59" s="9" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D59" s="9"/>
       <c r="E59" s="8"/>
@@ -3333,10 +3309,10 @@
         <v>13</v>
       </c>
       <c r="B60" s="8" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C60" s="9" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D60" s="9"/>
       <c r="E60" s="8"/>
@@ -3364,10 +3340,10 @@
         <v>13</v>
       </c>
       <c r="B61" s="8" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C61" s="9" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D61" s="9"/>
       <c r="E61" s="8"/>
@@ -3391,18 +3367,24 @@
       <c r="U61" s="8"/>
     </row>
     <row r="62" spans="1:21">
-      <c r="A62" s="21" t="s">
-        <v>79</v>
-      </c>
-      <c r="B62" s="8"/>
-      <c r="C62" s="9"/>
+      <c r="A62" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B62" s="8" t="s">
+        <v>240</v>
+      </c>
+      <c r="C62" s="9" t="s">
+        <v>73</v>
+      </c>
       <c r="D62" s="9"/>
       <c r="E62" s="8"/>
       <c r="F62" s="8"/>
       <c r="G62" s="9"/>
       <c r="H62" s="8"/>
       <c r="I62" s="8"/>
-      <c r="J62" s="7"/>
+      <c r="J62" s="7" t="s">
+        <v>14</v>
+      </c>
       <c r="K62" s="8"/>
       <c r="L62" s="8"/>
       <c r="M62" s="8"/>
@@ -3416,76 +3398,70 @@
       <c r="U62" s="8"/>
     </row>
     <row r="63" spans="1:21">
-      <c r="A63" s="19" t="s">
+      <c r="A63" s="21" t="s">
+        <v>79</v>
+      </c>
+      <c r="B63" s="8"/>
+      <c r="C63" s="9"/>
+      <c r="D63" s="9"/>
+      <c r="E63" s="8"/>
+      <c r="F63" s="8"/>
+      <c r="G63" s="9"/>
+      <c r="H63" s="8"/>
+      <c r="I63" s="8"/>
+      <c r="J63" s="7"/>
+      <c r="K63" s="8"/>
+      <c r="L63" s="8"/>
+      <c r="M63" s="8"/>
+      <c r="N63" s="8"/>
+      <c r="O63" s="8"/>
+      <c r="P63" s="8"/>
+      <c r="Q63" s="8"/>
+      <c r="R63" s="8"/>
+      <c r="S63" s="8"/>
+      <c r="T63" s="8"/>
+      <c r="U63" s="8"/>
+    </row>
+    <row r="64" spans="1:21">
+      <c r="A64" s="19" t="s">
         <v>66</v>
       </c>
-      <c r="B63" s="19" t="s">
+      <c r="B64" s="19" t="s">
         <v>100</v>
       </c>
-      <c r="C63" s="19" t="s">
+      <c r="C64" s="19" t="s">
         <v>114</v>
       </c>
-      <c r="D63" s="19"/>
-      <c r="E63" s="19"/>
-      <c r="F63" s="19"/>
-      <c r="G63" s="19"/>
-      <c r="H63" s="19" t="s">
-        <v>256</v>
-      </c>
-      <c r="I63" s="19"/>
-      <c r="J63" s="20"/>
-      <c r="K63" s="19"/>
-      <c r="L63" s="19"/>
-      <c r="M63" s="19"/>
-      <c r="N63" s="19"/>
-      <c r="O63" s="19"/>
-      <c r="P63" s="19"/>
-      <c r="Q63" s="19"/>
-      <c r="R63" s="19"/>
-      <c r="S63" s="19"/>
-      <c r="T63" s="19"/>
-      <c r="U63" s="19"/>
-    </row>
-    <row r="64" spans="1:21">
-      <c r="A64" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="B64" s="8" t="s">
-        <v>101</v>
-      </c>
-      <c r="C64" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="D64" s="9"/>
-      <c r="E64" s="8"/>
-      <c r="F64" s="8"/>
-      <c r="G64" s="9"/>
-      <c r="H64" s="8"/>
-      <c r="I64" s="8"/>
-      <c r="J64" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="K64" s="8"/>
-      <c r="L64" s="8"/>
-      <c r="M64" s="8"/>
-      <c r="N64" s="8"/>
-      <c r="O64" s="8"/>
-      <c r="P64" s="8"/>
-      <c r="Q64" s="8"/>
-      <c r="R64" s="8"/>
-      <c r="S64" s="8"/>
-      <c r="T64" s="8"/>
-      <c r="U64" s="8"/>
+      <c r="D64" s="19"/>
+      <c r="E64" s="19"/>
+      <c r="F64" s="19"/>
+      <c r="G64" s="19"/>
+      <c r="H64" s="19" t="s">
+        <v>255</v>
+      </c>
+      <c r="I64" s="19"/>
+      <c r="J64" s="20"/>
+      <c r="K64" s="19"/>
+      <c r="L64" s="19"/>
+      <c r="M64" s="19"/>
+      <c r="N64" s="19"/>
+      <c r="O64" s="19"/>
+      <c r="P64" s="19"/>
+      <c r="Q64" s="19"/>
+      <c r="R64" s="19"/>
+      <c r="S64" s="19"/>
+      <c r="T64" s="19"/>
+      <c r="U64" s="19"/>
     </row>
     <row r="65" spans="1:21">
       <c r="A65" s="8" t="s">
         <v>13</v>
       </c>
       <c r="B65" s="8" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C65" s="9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D65" s="9"/>
       <c r="E65" s="8"/>
@@ -3513,10 +3489,10 @@
         <v>13</v>
       </c>
       <c r="B66" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C66" s="9" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D66" s="9"/>
       <c r="E66" s="8"/>
@@ -3544,10 +3520,10 @@
         <v>13</v>
       </c>
       <c r="B67" s="8" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C67" s="9" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D67" s="9"/>
       <c r="E67" s="8"/>
@@ -3570,25 +3546,25 @@
       <c r="T67" s="8"/>
       <c r="U67" s="8"/>
     </row>
-    <row r="68" spans="1:21" ht="31.5">
+    <row r="68" spans="1:21">
       <c r="A68" s="8" t="s">
-        <v>78</v>
+        <v>13</v>
       </c>
       <c r="B68" s="8" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C68" s="9" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="D68" s="9"/>
       <c r="E68" s="8"/>
       <c r="F68" s="8"/>
       <c r="G68" s="9"/>
       <c r="H68" s="8"/>
-      <c r="I68" s="18" t="s">
-        <v>106</v>
-      </c>
-      <c r="J68" s="7"/>
+      <c r="I68" s="8"/>
+      <c r="J68" s="7" t="s">
+        <v>14</v>
+      </c>
       <c r="K68" s="8"/>
       <c r="L68" s="8"/>
       <c r="M68" s="8"/>
@@ -3606,10 +3582,10 @@
         <v>78</v>
       </c>
       <c r="B69" s="8" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C69" s="9" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D69" s="9"/>
       <c r="E69" s="8"/>
@@ -3617,7 +3593,7 @@
       <c r="G69" s="9"/>
       <c r="H69" s="8"/>
       <c r="I69" s="18" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="J69" s="7"/>
       <c r="K69" s="8"/>
@@ -3632,18 +3608,24 @@
       <c r="T69" s="8"/>
       <c r="U69" s="8"/>
     </row>
-    <row r="70" spans="1:21">
-      <c r="A70" s="21" t="s">
-        <v>79</v>
-      </c>
-      <c r="B70" s="8"/>
-      <c r="C70" s="9"/>
+    <row r="70" spans="1:21" ht="31.5">
+      <c r="A70" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="B70" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="C70" s="9" t="s">
+        <v>68</v>
+      </c>
       <c r="D70" s="9"/>
       <c r="E70" s="8"/>
       <c r="F70" s="8"/>
       <c r="G70" s="9"/>
       <c r="H70" s="8"/>
-      <c r="I70" s="8"/>
+      <c r="I70" s="18" t="s">
+        <v>108</v>
+      </c>
       <c r="J70" s="7"/>
       <c r="K70" s="8"/>
       <c r="L70" s="8"/>
@@ -3658,76 +3640,70 @@
       <c r="U70" s="8"/>
     </row>
     <row r="71" spans="1:21">
-      <c r="A71" s="19" t="s">
+      <c r="A71" s="21" t="s">
+        <v>79</v>
+      </c>
+      <c r="B71" s="8"/>
+      <c r="C71" s="9"/>
+      <c r="D71" s="9"/>
+      <c r="E71" s="8"/>
+      <c r="F71" s="8"/>
+      <c r="G71" s="9"/>
+      <c r="H71" s="8"/>
+      <c r="I71" s="8"/>
+      <c r="J71" s="7"/>
+      <c r="K71" s="8"/>
+      <c r="L71" s="8"/>
+      <c r="M71" s="8"/>
+      <c r="N71" s="8"/>
+      <c r="O71" s="8"/>
+      <c r="P71" s="8"/>
+      <c r="Q71" s="8"/>
+      <c r="R71" s="8"/>
+      <c r="S71" s="8"/>
+      <c r="T71" s="8"/>
+      <c r="U71" s="8"/>
+    </row>
+    <row r="72" spans="1:21">
+      <c r="A72" s="19" t="s">
         <v>66</v>
       </c>
-      <c r="B71" s="19" t="s">
-        <v>278</v>
-      </c>
-      <c r="C71" s="19" t="s">
-        <v>272</v>
-      </c>
-      <c r="D71" s="19"/>
-      <c r="E71" s="19"/>
-      <c r="F71" s="19"/>
-      <c r="G71" s="19"/>
-      <c r="H71" s="19" t="s">
-        <v>256</v>
-      </c>
-      <c r="I71" s="19"/>
-      <c r="J71" s="20"/>
-      <c r="K71" s="19"/>
-      <c r="L71" s="19"/>
-      <c r="M71" s="19"/>
-      <c r="N71" s="19"/>
-      <c r="O71" s="19"/>
-      <c r="P71" s="19"/>
-      <c r="Q71" s="19"/>
-      <c r="R71" s="19"/>
-      <c r="S71" s="19"/>
-      <c r="T71" s="19"/>
-      <c r="U71" s="19"/>
-    </row>
-    <row r="72" spans="1:21">
-      <c r="A72" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="B72" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="C72" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="D72" s="9"/>
-      <c r="E72" s="8"/>
-      <c r="F72" s="8"/>
-      <c r="G72" s="9"/>
-      <c r="H72" s="8"/>
-      <c r="I72" s="8"/>
-      <c r="J72" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="K72" s="8"/>
-      <c r="L72" s="8"/>
-      <c r="M72" s="8"/>
-      <c r="N72" s="8"/>
-      <c r="O72" s="8"/>
-      <c r="P72" s="8"/>
-      <c r="Q72" s="8"/>
-      <c r="R72" s="8"/>
-      <c r="S72" s="8"/>
-      <c r="T72" s="8"/>
-      <c r="U72" s="8"/>
+      <c r="B72" s="19" t="s">
+        <v>275</v>
+      </c>
+      <c r="C72" s="19" t="s">
+        <v>269</v>
+      </c>
+      <c r="D72" s="19"/>
+      <c r="E72" s="19"/>
+      <c r="F72" s="19"/>
+      <c r="G72" s="19"/>
+      <c r="H72" s="19" t="s">
+        <v>255</v>
+      </c>
+      <c r="I72" s="19"/>
+      <c r="J72" s="20"/>
+      <c r="K72" s="19"/>
+      <c r="L72" s="19"/>
+      <c r="M72" s="19"/>
+      <c r="N72" s="19"/>
+      <c r="O72" s="19"/>
+      <c r="P72" s="19"/>
+      <c r="Q72" s="19"/>
+      <c r="R72" s="19"/>
+      <c r="S72" s="19"/>
+      <c r="T72" s="19"/>
+      <c r="U72" s="19"/>
     </row>
     <row r="73" spans="1:21">
       <c r="A73" s="8" t="s">
         <v>13</v>
       </c>
       <c r="B73" s="8" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C73" s="9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D73" s="9"/>
       <c r="E73" s="8"/>
@@ -3755,10 +3731,10 @@
         <v>13</v>
       </c>
       <c r="B74" s="8" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C74" s="9" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D74" s="9"/>
       <c r="E74" s="8"/>
@@ -3786,10 +3762,10 @@
         <v>13</v>
       </c>
       <c r="B75" s="8" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C75" s="9" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D75" s="9"/>
       <c r="E75" s="8"/>
@@ -3817,10 +3793,10 @@
         <v>13</v>
       </c>
       <c r="B76" s="8" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C76" s="9" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D76" s="9"/>
       <c r="E76" s="8"/>
@@ -3844,18 +3820,24 @@
       <c r="U76" s="8"/>
     </row>
     <row r="77" spans="1:21">
-      <c r="A77" s="21" t="s">
-        <v>79</v>
-      </c>
-      <c r="B77" s="8"/>
-      <c r="C77" s="9"/>
+      <c r="A77" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B77" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="C77" s="9" t="s">
+        <v>73</v>
+      </c>
       <c r="D77" s="9"/>
       <c r="E77" s="8"/>
       <c r="F77" s="8"/>
       <c r="G77" s="9"/>
       <c r="H77" s="8"/>
       <c r="I77" s="8"/>
-      <c r="J77" s="7"/>
+      <c r="J77" s="7" t="s">
+        <v>14</v>
+      </c>
       <c r="K77" s="8"/>
       <c r="L77" s="8"/>
       <c r="M77" s="8"/>
@@ -3869,76 +3851,70 @@
       <c r="U77" s="8"/>
     </row>
     <row r="78" spans="1:21">
-      <c r="A78" s="22" t="s">
+      <c r="A78" s="21" t="s">
+        <v>79</v>
+      </c>
+      <c r="B78" s="8"/>
+      <c r="C78" s="9"/>
+      <c r="D78" s="9"/>
+      <c r="E78" s="8"/>
+      <c r="F78" s="8"/>
+      <c r="G78" s="9"/>
+      <c r="H78" s="8"/>
+      <c r="I78" s="8"/>
+      <c r="J78" s="7"/>
+      <c r="K78" s="8"/>
+      <c r="L78" s="8"/>
+      <c r="M78" s="8"/>
+      <c r="N78" s="8"/>
+      <c r="O78" s="8"/>
+      <c r="P78" s="8"/>
+      <c r="Q78" s="8"/>
+      <c r="R78" s="8"/>
+      <c r="S78" s="8"/>
+      <c r="T78" s="8"/>
+      <c r="U78" s="8"/>
+    </row>
+    <row r="79" spans="1:21">
+      <c r="A79" s="22" t="s">
         <v>66</v>
       </c>
-      <c r="B78" s="19" t="s">
+      <c r="B79" s="19" t="s">
         <v>115</v>
       </c>
-      <c r="C78" s="19" t="s">
+      <c r="C79" s="19" t="s">
         <v>129</v>
       </c>
-      <c r="D78" s="19"/>
-      <c r="E78" s="19"/>
-      <c r="F78" s="19"/>
-      <c r="G78" s="19"/>
-      <c r="H78" s="19" t="s">
-        <v>258</v>
-      </c>
-      <c r="I78" s="19"/>
-      <c r="J78" s="20"/>
-      <c r="K78" s="19"/>
-      <c r="L78" s="19"/>
-      <c r="M78" s="19"/>
-      <c r="N78" s="19"/>
-      <c r="O78" s="19"/>
-      <c r="P78" s="19"/>
-      <c r="Q78" s="19"/>
-      <c r="R78" s="19"/>
-      <c r="S78" s="19"/>
-      <c r="T78" s="19"/>
-      <c r="U78" s="19"/>
-    </row>
-    <row r="79" spans="1:21">
-      <c r="A79" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="B79" s="8" t="s">
-        <v>116</v>
-      </c>
-      <c r="C79" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="D79" s="9"/>
-      <c r="E79" s="8"/>
-      <c r="F79" s="8"/>
-      <c r="G79" s="9"/>
-      <c r="H79" s="8"/>
-      <c r="I79" s="8"/>
-      <c r="J79" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="K79" s="8"/>
-      <c r="L79" s="8"/>
-      <c r="M79" s="8"/>
-      <c r="N79" s="8"/>
-      <c r="O79" s="8"/>
-      <c r="P79" s="8"/>
-      <c r="Q79" s="8"/>
-      <c r="R79" s="8"/>
-      <c r="S79" s="8"/>
-      <c r="T79" s="8"/>
-      <c r="U79" s="8"/>
+      <c r="D79" s="19"/>
+      <c r="E79" s="19"/>
+      <c r="F79" s="19"/>
+      <c r="G79" s="19"/>
+      <c r="H79" s="19" t="s">
+        <v>257</v>
+      </c>
+      <c r="I79" s="19"/>
+      <c r="J79" s="20"/>
+      <c r="K79" s="19"/>
+      <c r="L79" s="19"/>
+      <c r="M79" s="19"/>
+      <c r="N79" s="19"/>
+      <c r="O79" s="19"/>
+      <c r="P79" s="19"/>
+      <c r="Q79" s="19"/>
+      <c r="R79" s="19"/>
+      <c r="S79" s="19"/>
+      <c r="T79" s="19"/>
+      <c r="U79" s="19"/>
     </row>
     <row r="80" spans="1:21">
       <c r="A80" s="21" t="s">
         <v>13</v>
       </c>
       <c r="B80" s="8" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C80" s="9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D80" s="9"/>
       <c r="E80" s="8"/>
@@ -3966,10 +3942,10 @@
         <v>13</v>
       </c>
       <c r="B81" s="8" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C81" s="9" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D81" s="9"/>
       <c r="E81" s="8"/>
@@ -3997,10 +3973,10 @@
         <v>13</v>
       </c>
       <c r="B82" s="8" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C82" s="9" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D82" s="9"/>
       <c r="E82" s="8"/>
@@ -4025,23 +4001,23 @@
     </row>
     <row r="83" spans="1:21">
       <c r="A83" s="21" t="s">
-        <v>78</v>
+        <v>13</v>
       </c>
       <c r="B83" s="8" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C83" s="9" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="D83" s="9"/>
       <c r="E83" s="8"/>
       <c r="F83" s="8"/>
       <c r="G83" s="9"/>
       <c r="H83" s="8"/>
-      <c r="I83" s="8" t="s">
-        <v>121</v>
-      </c>
-      <c r="J83" s="7"/>
+      <c r="I83" s="8"/>
+      <c r="J83" s="7" t="s">
+        <v>14</v>
+      </c>
       <c r="K83" s="8"/>
       <c r="L83" s="8"/>
       <c r="M83" s="8"/>
@@ -4059,10 +4035,10 @@
         <v>78</v>
       </c>
       <c r="B84" s="8" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C84" s="9" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D84" s="9"/>
       <c r="E84" s="8"/>
@@ -4070,7 +4046,7 @@
       <c r="G84" s="9"/>
       <c r="H84" s="8"/>
       <c r="I84" s="8" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="J84" s="7"/>
       <c r="K84" s="8"/>
@@ -4087,16 +4063,22 @@
     </row>
     <row r="85" spans="1:21">
       <c r="A85" s="21" t="s">
-        <v>79</v>
-      </c>
-      <c r="B85" s="8"/>
-      <c r="C85" s="9"/>
+        <v>78</v>
+      </c>
+      <c r="B85" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="C85" s="9" t="s">
+        <v>68</v>
+      </c>
       <c r="D85" s="9"/>
       <c r="E85" s="8"/>
       <c r="F85" s="8"/>
       <c r="G85" s="9"/>
       <c r="H85" s="8"/>
-      <c r="I85" s="8"/>
+      <c r="I85" s="8" t="s">
+        <v>123</v>
+      </c>
       <c r="J85" s="7"/>
       <c r="K85" s="8"/>
       <c r="L85" s="8"/>
@@ -4111,76 +4093,70 @@
       <c r="U85" s="8"/>
     </row>
     <row r="86" spans="1:21">
-      <c r="A86" s="22" t="s">
+      <c r="A86" s="21" t="s">
+        <v>79</v>
+      </c>
+      <c r="B86" s="8"/>
+      <c r="C86" s="9"/>
+      <c r="D86" s="9"/>
+      <c r="E86" s="8"/>
+      <c r="F86" s="8"/>
+      <c r="G86" s="9"/>
+      <c r="H86" s="8"/>
+      <c r="I86" s="8"/>
+      <c r="J86" s="7"/>
+      <c r="K86" s="8"/>
+      <c r="L86" s="8"/>
+      <c r="M86" s="8"/>
+      <c r="N86" s="8"/>
+      <c r="O86" s="8"/>
+      <c r="P86" s="8"/>
+      <c r="Q86" s="8"/>
+      <c r="R86" s="8"/>
+      <c r="S86" s="8"/>
+      <c r="T86" s="8"/>
+      <c r="U86" s="8"/>
+    </row>
+    <row r="87" spans="1:21">
+      <c r="A87" s="22" t="s">
         <v>66</v>
       </c>
-      <c r="B86" s="19" t="s">
-        <v>279</v>
-      </c>
-      <c r="C86" s="19" t="s">
-        <v>262</v>
-      </c>
-      <c r="D86" s="19"/>
-      <c r="E86" s="19"/>
-      <c r="F86" s="19"/>
-      <c r="G86" s="19"/>
-      <c r="H86" s="19" t="s">
-        <v>258</v>
-      </c>
-      <c r="I86" s="19"/>
-      <c r="J86" s="20"/>
-      <c r="K86" s="19"/>
-      <c r="L86" s="19"/>
-      <c r="M86" s="19"/>
-      <c r="N86" s="19"/>
-      <c r="O86" s="19"/>
-      <c r="P86" s="19"/>
-      <c r="Q86" s="19"/>
-      <c r="R86" s="19"/>
-      <c r="S86" s="19"/>
-      <c r="T86" s="19"/>
-      <c r="U86" s="19"/>
-    </row>
-    <row r="87" spans="1:21">
-      <c r="A87" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="B87" s="8" t="s">
-        <v>124</v>
-      </c>
-      <c r="C87" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="D87" s="9"/>
-      <c r="E87" s="8"/>
-      <c r="F87" s="8"/>
-      <c r="G87" s="9"/>
-      <c r="H87" s="8"/>
-      <c r="I87" s="8"/>
-      <c r="J87" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="K87" s="8"/>
-      <c r="L87" s="8"/>
-      <c r="M87" s="8"/>
-      <c r="N87" s="8"/>
-      <c r="O87" s="8"/>
-      <c r="P87" s="8"/>
-      <c r="Q87" s="8"/>
-      <c r="R87" s="8"/>
-      <c r="S87" s="8"/>
-      <c r="T87" s="8"/>
-      <c r="U87" s="8"/>
+      <c r="B87" s="19" t="s">
+        <v>276</v>
+      </c>
+      <c r="C87" s="19" t="s">
+        <v>261</v>
+      </c>
+      <c r="D87" s="19"/>
+      <c r="E87" s="19"/>
+      <c r="F87" s="19"/>
+      <c r="G87" s="19"/>
+      <c r="H87" s="19" t="s">
+        <v>257</v>
+      </c>
+      <c r="I87" s="19"/>
+      <c r="J87" s="20"/>
+      <c r="K87" s="19"/>
+      <c r="L87" s="19"/>
+      <c r="M87" s="19"/>
+      <c r="N87" s="19"/>
+      <c r="O87" s="19"/>
+      <c r="P87" s="19"/>
+      <c r="Q87" s="19"/>
+      <c r="R87" s="19"/>
+      <c r="S87" s="19"/>
+      <c r="T87" s="19"/>
+      <c r="U87" s="19"/>
     </row>
     <row r="88" spans="1:21">
       <c r="A88" s="21" t="s">
         <v>13</v>
       </c>
       <c r="B88" s="8" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C88" s="9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D88" s="9"/>
       <c r="E88" s="8"/>
@@ -4208,10 +4184,10 @@
         <v>13</v>
       </c>
       <c r="B89" s="8" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C89" s="9" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D89" s="9"/>
       <c r="E89" s="8"/>
@@ -4239,10 +4215,10 @@
         <v>13</v>
       </c>
       <c r="B90" s="8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C90" s="9" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D90" s="9"/>
       <c r="E90" s="8"/>
@@ -4270,10 +4246,10 @@
         <v>13</v>
       </c>
       <c r="B91" s="8" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C91" s="9" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D91" s="9"/>
       <c r="E91" s="8"/>
@@ -4298,17 +4274,23 @@
     </row>
     <row r="92" spans="1:21">
       <c r="A92" s="21" t="s">
-        <v>79</v>
-      </c>
-      <c r="B92" s="8"/>
-      <c r="C92" s="9"/>
+        <v>13</v>
+      </c>
+      <c r="B92" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="C92" s="9" t="s">
+        <v>73</v>
+      </c>
       <c r="D92" s="9"/>
       <c r="E92" s="8"/>
       <c r="F92" s="8"/>
       <c r="G92" s="9"/>
       <c r="H92" s="8"/>
       <c r="I92" s="8"/>
-      <c r="J92" s="7"/>
+      <c r="J92" s="7" t="s">
+        <v>14</v>
+      </c>
       <c r="K92" s="8"/>
       <c r="L92" s="8"/>
       <c r="M92" s="8"/>
@@ -4322,76 +4304,70 @@
       <c r="U92" s="8"/>
     </row>
     <row r="93" spans="1:21">
-      <c r="A93" s="22" t="s">
+      <c r="A93" s="21" t="s">
+        <v>79</v>
+      </c>
+      <c r="B93" s="8"/>
+      <c r="C93" s="9"/>
+      <c r="D93" s="9"/>
+      <c r="E93" s="8"/>
+      <c r="F93" s="8"/>
+      <c r="G93" s="9"/>
+      <c r="H93" s="8"/>
+      <c r="I93" s="8"/>
+      <c r="J93" s="7"/>
+      <c r="K93" s="8"/>
+      <c r="L93" s="8"/>
+      <c r="M93" s="8"/>
+      <c r="N93" s="8"/>
+      <c r="O93" s="8"/>
+      <c r="P93" s="8"/>
+      <c r="Q93" s="8"/>
+      <c r="R93" s="8"/>
+      <c r="S93" s="8"/>
+      <c r="T93" s="8"/>
+      <c r="U93" s="8"/>
+    </row>
+    <row r="94" spans="1:21">
+      <c r="A94" s="22" t="s">
         <v>66</v>
       </c>
-      <c r="B93" s="19" t="s">
+      <c r="B94" s="19" t="s">
         <v>135</v>
       </c>
-      <c r="C93" s="19" t="s">
+      <c r="C94" s="19" t="s">
         <v>134</v>
       </c>
-      <c r="D93" s="19"/>
-      <c r="E93" s="19"/>
-      <c r="F93" s="19"/>
-      <c r="G93" s="19"/>
-      <c r="H93" s="19" t="s">
-        <v>248</v>
-      </c>
-      <c r="I93" s="19"/>
-      <c r="J93" s="20"/>
-      <c r="K93" s="19"/>
-      <c r="L93" s="19"/>
-      <c r="M93" s="19"/>
-      <c r="N93" s="19"/>
-      <c r="O93" s="19"/>
-      <c r="P93" s="19"/>
-      <c r="Q93" s="19"/>
-      <c r="R93" s="19"/>
-      <c r="S93" s="19"/>
-      <c r="T93" s="19"/>
-      <c r="U93" s="19"/>
-    </row>
-    <row r="94" spans="1:21">
-      <c r="A94" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="B94" s="8" t="s">
-        <v>132</v>
-      </c>
-      <c r="C94" s="9" t="s">
-        <v>130</v>
-      </c>
-      <c r="D94" s="9"/>
-      <c r="E94" s="8"/>
-      <c r="F94" s="8"/>
-      <c r="G94" s="9"/>
-      <c r="H94" s="8"/>
-      <c r="I94" s="8"/>
-      <c r="J94" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="K94" s="8"/>
-      <c r="L94" s="8"/>
-      <c r="M94" s="8"/>
-      <c r="N94" s="8"/>
-      <c r="O94" s="8"/>
-      <c r="P94" s="8"/>
-      <c r="Q94" s="8"/>
-      <c r="R94" s="8"/>
-      <c r="S94" s="8"/>
-      <c r="T94" s="8"/>
-      <c r="U94" s="8"/>
+      <c r="D94" s="19"/>
+      <c r="E94" s="19"/>
+      <c r="F94" s="19"/>
+      <c r="G94" s="19"/>
+      <c r="H94" s="19" t="s">
+        <v>247</v>
+      </c>
+      <c r="I94" s="19"/>
+      <c r="J94" s="20"/>
+      <c r="K94" s="19"/>
+      <c r="L94" s="19"/>
+      <c r="M94" s="19"/>
+      <c r="N94" s="19"/>
+      <c r="O94" s="19"/>
+      <c r="P94" s="19"/>
+      <c r="Q94" s="19"/>
+      <c r="R94" s="19"/>
+      <c r="S94" s="19"/>
+      <c r="T94" s="19"/>
+      <c r="U94" s="19"/>
     </row>
     <row r="95" spans="1:21">
       <c r="A95" s="21" t="s">
         <v>13</v>
       </c>
       <c r="B95" s="8" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C95" s="9" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D95" s="9"/>
       <c r="E95" s="8"/>
@@ -4416,17 +4392,23 @@
     </row>
     <row r="96" spans="1:21">
       <c r="A96" s="21" t="s">
-        <v>79</v>
-      </c>
-      <c r="B96" s="8"/>
-      <c r="C96" s="9"/>
+        <v>13</v>
+      </c>
+      <c r="B96" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="C96" s="9" t="s">
+        <v>131</v>
+      </c>
       <c r="D96" s="9"/>
       <c r="E96" s="8"/>
       <c r="F96" s="8"/>
       <c r="G96" s="9"/>
       <c r="H96" s="8"/>
       <c r="I96" s="8"/>
-      <c r="J96" s="7"/>
+      <c r="J96" s="7" t="s">
+        <v>14</v>
+      </c>
       <c r="K96" s="8"/>
       <c r="L96" s="8"/>
       <c r="M96" s="8"/>
@@ -4440,76 +4422,70 @@
       <c r="U96" s="8"/>
     </row>
     <row r="97" spans="1:21">
-      <c r="A97" s="22" t="s">
+      <c r="A97" s="21" t="s">
+        <v>79</v>
+      </c>
+      <c r="B97" s="8"/>
+      <c r="C97" s="9"/>
+      <c r="D97" s="9"/>
+      <c r="E97" s="8"/>
+      <c r="F97" s="8"/>
+      <c r="G97" s="9"/>
+      <c r="H97" s="8"/>
+      <c r="I97" s="8"/>
+      <c r="J97" s="7"/>
+      <c r="K97" s="8"/>
+      <c r="L97" s="8"/>
+      <c r="M97" s="8"/>
+      <c r="N97" s="8"/>
+      <c r="O97" s="8"/>
+      <c r="P97" s="8"/>
+      <c r="Q97" s="8"/>
+      <c r="R97" s="8"/>
+      <c r="S97" s="8"/>
+      <c r="T97" s="8"/>
+      <c r="U97" s="8"/>
+    </row>
+    <row r="98" spans="1:21">
+      <c r="A98" s="22" t="s">
         <v>66</v>
       </c>
-      <c r="B97" s="19" t="s">
-        <v>280</v>
-      </c>
-      <c r="C97" s="19" t="s">
-        <v>263</v>
-      </c>
-      <c r="D97" s="19"/>
-      <c r="E97" s="19"/>
-      <c r="F97" s="19"/>
-      <c r="G97" s="19"/>
-      <c r="H97" s="19" t="s">
-        <v>248</v>
-      </c>
-      <c r="I97" s="19"/>
-      <c r="J97" s="20"/>
-      <c r="K97" s="19"/>
-      <c r="L97" s="19"/>
-      <c r="M97" s="19"/>
-      <c r="N97" s="19"/>
-      <c r="O97" s="19"/>
-      <c r="P97" s="19"/>
-      <c r="Q97" s="19"/>
-      <c r="R97" s="19"/>
-      <c r="S97" s="19"/>
-      <c r="T97" s="19"/>
-      <c r="U97" s="19"/>
-    </row>
-    <row r="98" spans="1:21">
-      <c r="A98" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="B98" s="8" t="s">
-        <v>136</v>
-      </c>
-      <c r="C98" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="D98" s="9"/>
-      <c r="E98" s="8"/>
-      <c r="F98" s="8"/>
-      <c r="G98" s="9"/>
-      <c r="H98" s="8"/>
-      <c r="I98" s="8"/>
-      <c r="J98" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="K98" s="8"/>
-      <c r="L98" s="8"/>
-      <c r="M98" s="8"/>
-      <c r="N98" s="8"/>
-      <c r="O98" s="8"/>
-      <c r="P98" s="8"/>
-      <c r="Q98" s="8"/>
-      <c r="R98" s="8"/>
-      <c r="S98" s="8"/>
-      <c r="T98" s="8"/>
-      <c r="U98" s="8"/>
+      <c r="B98" s="19" t="s">
+        <v>277</v>
+      </c>
+      <c r="C98" s="19" t="s">
+        <v>262</v>
+      </c>
+      <c r="D98" s="19"/>
+      <c r="E98" s="19"/>
+      <c r="F98" s="19"/>
+      <c r="G98" s="19"/>
+      <c r="H98" s="19" t="s">
+        <v>247</v>
+      </c>
+      <c r="I98" s="19"/>
+      <c r="J98" s="20"/>
+      <c r="K98" s="19"/>
+      <c r="L98" s="19"/>
+      <c r="M98" s="19"/>
+      <c r="N98" s="19"/>
+      <c r="O98" s="19"/>
+      <c r="P98" s="19"/>
+      <c r="Q98" s="19"/>
+      <c r="R98" s="19"/>
+      <c r="S98" s="19"/>
+      <c r="T98" s="19"/>
+      <c r="U98" s="19"/>
     </row>
     <row r="99" spans="1:21">
       <c r="A99" s="21" t="s">
         <v>13</v>
       </c>
       <c r="B99" s="8" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C99" s="9" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D99" s="9"/>
       <c r="E99" s="8"/>
@@ -4537,10 +4513,10 @@
         <v>13</v>
       </c>
       <c r="B100" s="8" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C100" s="9" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D100" s="9"/>
       <c r="E100" s="8"/>
@@ -4565,17 +4541,23 @@
     </row>
     <row r="101" spans="1:21">
       <c r="A101" s="21" t="s">
-        <v>79</v>
-      </c>
-      <c r="B101" s="8"/>
-      <c r="C101" s="9"/>
+        <v>13</v>
+      </c>
+      <c r="B101" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="C101" s="9" t="s">
+        <v>73</v>
+      </c>
       <c r="D101" s="9"/>
       <c r="E101" s="8"/>
       <c r="F101" s="8"/>
       <c r="G101" s="9"/>
       <c r="H101" s="8"/>
       <c r="I101" s="8"/>
-      <c r="J101" s="7"/>
+      <c r="J101" s="7" t="s">
+        <v>14</v>
+      </c>
       <c r="K101" s="8"/>
       <c r="L101" s="8"/>
       <c r="M101" s="8"/>
@@ -4589,76 +4571,70 @@
       <c r="U101" s="8"/>
     </row>
     <row r="102" spans="1:21">
-      <c r="A102" s="22" t="s">
+      <c r="A102" s="21" t="s">
+        <v>79</v>
+      </c>
+      <c r="B102" s="8"/>
+      <c r="C102" s="9"/>
+      <c r="D102" s="9"/>
+      <c r="E102" s="8"/>
+      <c r="F102" s="8"/>
+      <c r="G102" s="9"/>
+      <c r="H102" s="8"/>
+      <c r="I102" s="8"/>
+      <c r="J102" s="7"/>
+      <c r="K102" s="8"/>
+      <c r="L102" s="8"/>
+      <c r="M102" s="8"/>
+      <c r="N102" s="8"/>
+      <c r="O102" s="8"/>
+      <c r="P102" s="8"/>
+      <c r="Q102" s="8"/>
+      <c r="R102" s="8"/>
+      <c r="S102" s="8"/>
+      <c r="T102" s="8"/>
+      <c r="U102" s="8"/>
+    </row>
+    <row r="103" spans="1:21">
+      <c r="A103" s="22" t="s">
         <v>66</v>
       </c>
-      <c r="B102" s="19" t="s">
+      <c r="B103" s="19" t="s">
         <v>139</v>
       </c>
-      <c r="C102" s="19" t="s">
+      <c r="C103" s="19" t="s">
         <v>195</v>
       </c>
-      <c r="D102" s="19"/>
-      <c r="E102" s="19"/>
-      <c r="F102" s="19"/>
-      <c r="G102" s="19"/>
-      <c r="H102" s="19" t="s">
-        <v>247</v>
-      </c>
-      <c r="I102" s="19"/>
-      <c r="J102" s="20"/>
-      <c r="K102" s="19"/>
-      <c r="L102" s="19"/>
-      <c r="M102" s="19"/>
-      <c r="N102" s="19"/>
-      <c r="O102" s="19"/>
-      <c r="P102" s="19"/>
-      <c r="Q102" s="19"/>
-      <c r="R102" s="19"/>
-      <c r="S102" s="19"/>
-      <c r="T102" s="19"/>
-      <c r="U102" s="19"/>
-    </row>
-    <row r="103" spans="1:21">
-      <c r="A103" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="B103" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="C103" s="9" t="s">
-        <v>147</v>
-      </c>
-      <c r="D103" s="9"/>
-      <c r="E103" s="8"/>
-      <c r="F103" s="8"/>
-      <c r="G103" s="9"/>
-      <c r="H103" s="8"/>
-      <c r="I103" s="8"/>
-      <c r="J103" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="K103" s="8"/>
-      <c r="L103" s="8"/>
-      <c r="M103" s="8"/>
-      <c r="N103" s="8"/>
-      <c r="O103" s="8"/>
-      <c r="P103" s="8"/>
-      <c r="Q103" s="8"/>
-      <c r="R103" s="8"/>
-      <c r="S103" s="8"/>
-      <c r="T103" s="8"/>
-      <c r="U103" s="8"/>
+      <c r="D103" s="19"/>
+      <c r="E103" s="19"/>
+      <c r="F103" s="19"/>
+      <c r="G103" s="19"/>
+      <c r="H103" s="19" t="s">
+        <v>246</v>
+      </c>
+      <c r="I103" s="19"/>
+      <c r="J103" s="20"/>
+      <c r="K103" s="19"/>
+      <c r="L103" s="19"/>
+      <c r="M103" s="19"/>
+      <c r="N103" s="19"/>
+      <c r="O103" s="19"/>
+      <c r="P103" s="19"/>
+      <c r="Q103" s="19"/>
+      <c r="R103" s="19"/>
+      <c r="S103" s="19"/>
+      <c r="T103" s="19"/>
+      <c r="U103" s="19"/>
     </row>
     <row r="104" spans="1:21">
       <c r="A104" s="21" t="s">
         <v>13</v>
       </c>
       <c r="B104" s="8" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C104" s="9" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D104" s="9"/>
       <c r="E104" s="8"/>
@@ -4686,10 +4662,10 @@
         <v>13</v>
       </c>
       <c r="B105" s="8" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C105" s="9" t="s">
-        <v>69</v>
+        <v>148</v>
       </c>
       <c r="D105" s="9"/>
       <c r="E105" s="8"/>
@@ -4714,17 +4690,23 @@
     </row>
     <row r="106" spans="1:21">
       <c r="A106" s="21" t="s">
-        <v>79</v>
-      </c>
-      <c r="B106" s="8"/>
-      <c r="C106" s="9"/>
+        <v>13</v>
+      </c>
+      <c r="B106" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="C106" s="9" t="s">
+        <v>69</v>
+      </c>
       <c r="D106" s="9"/>
       <c r="E106" s="8"/>
       <c r="F106" s="8"/>
       <c r="G106" s="9"/>
       <c r="H106" s="8"/>
       <c r="I106" s="8"/>
-      <c r="J106" s="7"/>
+      <c r="J106" s="7" t="s">
+        <v>14</v>
+      </c>
       <c r="K106" s="8"/>
       <c r="L106" s="8"/>
       <c r="M106" s="8"/>
@@ -4738,76 +4720,70 @@
       <c r="U106" s="8"/>
     </row>
     <row r="107" spans="1:21">
-      <c r="A107" s="22" t="s">
+      <c r="A107" s="21" t="s">
+        <v>79</v>
+      </c>
+      <c r="B107" s="8"/>
+      <c r="C107" s="9"/>
+      <c r="D107" s="9"/>
+      <c r="E107" s="8"/>
+      <c r="F107" s="8"/>
+      <c r="G107" s="9"/>
+      <c r="H107" s="8"/>
+      <c r="I107" s="8"/>
+      <c r="J107" s="7"/>
+      <c r="K107" s="8"/>
+      <c r="L107" s="8"/>
+      <c r="M107" s="8"/>
+      <c r="N107" s="8"/>
+      <c r="O107" s="8"/>
+      <c r="P107" s="8"/>
+      <c r="Q107" s="8"/>
+      <c r="R107" s="8"/>
+      <c r="S107" s="8"/>
+      <c r="T107" s="8"/>
+      <c r="U107" s="8"/>
+    </row>
+    <row r="108" spans="1:21">
+      <c r="A108" s="22" t="s">
         <v>66</v>
       </c>
-      <c r="B107" s="19" t="s">
-        <v>281</v>
-      </c>
-      <c r="C107" s="19" t="s">
-        <v>271</v>
-      </c>
-      <c r="D107" s="19"/>
-      <c r="E107" s="19"/>
-      <c r="F107" s="19"/>
-      <c r="G107" s="19"/>
-      <c r="H107" s="19" t="s">
-        <v>247</v>
-      </c>
-      <c r="I107" s="19"/>
-      <c r="J107" s="20"/>
-      <c r="K107" s="19"/>
-      <c r="L107" s="19"/>
-      <c r="M107" s="19"/>
-      <c r="N107" s="19"/>
-      <c r="O107" s="19"/>
-      <c r="P107" s="19"/>
-      <c r="Q107" s="19"/>
-      <c r="R107" s="19"/>
-      <c r="S107" s="19"/>
-      <c r="T107" s="19"/>
-      <c r="U107" s="19"/>
-    </row>
-    <row r="108" spans="1:21">
-      <c r="A108" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="B108" s="8" t="s">
-        <v>143</v>
-      </c>
-      <c r="C108" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="D108" s="9"/>
-      <c r="E108" s="8"/>
-      <c r="F108" s="8"/>
-      <c r="G108" s="9"/>
-      <c r="H108" s="8"/>
-      <c r="I108" s="8"/>
-      <c r="J108" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="K108" s="8"/>
-      <c r="L108" s="8"/>
-      <c r="M108" s="8"/>
-      <c r="N108" s="8"/>
-      <c r="O108" s="8"/>
-      <c r="P108" s="8"/>
-      <c r="Q108" s="8"/>
-      <c r="R108" s="8"/>
-      <c r="S108" s="8"/>
-      <c r="T108" s="8"/>
-      <c r="U108" s="8"/>
+      <c r="B108" s="19" t="s">
+        <v>278</v>
+      </c>
+      <c r="C108" s="19" t="s">
+        <v>268</v>
+      </c>
+      <c r="D108" s="19"/>
+      <c r="E108" s="19"/>
+      <c r="F108" s="19"/>
+      <c r="G108" s="19"/>
+      <c r="H108" s="19" t="s">
+        <v>246</v>
+      </c>
+      <c r="I108" s="19"/>
+      <c r="J108" s="20"/>
+      <c r="K108" s="19"/>
+      <c r="L108" s="19"/>
+      <c r="M108" s="19"/>
+      <c r="N108" s="19"/>
+      <c r="O108" s="19"/>
+      <c r="P108" s="19"/>
+      <c r="Q108" s="19"/>
+      <c r="R108" s="19"/>
+      <c r="S108" s="19"/>
+      <c r="T108" s="19"/>
+      <c r="U108" s="19"/>
     </row>
     <row r="109" spans="1:21">
       <c r="A109" s="21" t="s">
         <v>13</v>
       </c>
       <c r="B109" s="8" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C109" s="9" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D109" s="9"/>
       <c r="E109" s="8"/>
@@ -4835,10 +4811,10 @@
         <v>13</v>
       </c>
       <c r="B110" s="8" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C110" s="9" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D110" s="9"/>
       <c r="E110" s="8"/>
@@ -4866,10 +4842,10 @@
         <v>13</v>
       </c>
       <c r="B111" s="8" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C111" s="9" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D111" s="9"/>
       <c r="E111" s="8"/>
@@ -4894,17 +4870,23 @@
     </row>
     <row r="112" spans="1:21">
       <c r="A112" s="21" t="s">
-        <v>79</v>
-      </c>
-      <c r="B112" s="8"/>
-      <c r="C112" s="9"/>
+        <v>13</v>
+      </c>
+      <c r="B112" s="8" t="s">
+        <v>146</v>
+      </c>
+      <c r="C112" s="9" t="s">
+        <v>73</v>
+      </c>
       <c r="D112" s="9"/>
       <c r="E112" s="8"/>
       <c r="F112" s="8"/>
       <c r="G112" s="9"/>
       <c r="H112" s="8"/>
       <c r="I112" s="8"/>
-      <c r="J112" s="7"/>
+      <c r="J112" s="7" t="s">
+        <v>14</v>
+      </c>
       <c r="K112" s="8"/>
       <c r="L112" s="8"/>
       <c r="M112" s="8"/>
@@ -4918,76 +4900,70 @@
       <c r="U112" s="8"/>
     </row>
     <row r="113" spans="1:21">
-      <c r="A113" s="22" t="s">
+      <c r="A113" s="21" t="s">
+        <v>79</v>
+      </c>
+      <c r="B113" s="8"/>
+      <c r="C113" s="9"/>
+      <c r="D113" s="9"/>
+      <c r="E113" s="8"/>
+      <c r="F113" s="8"/>
+      <c r="G113" s="9"/>
+      <c r="H113" s="8"/>
+      <c r="I113" s="8"/>
+      <c r="J113" s="7"/>
+      <c r="K113" s="8"/>
+      <c r="L113" s="8"/>
+      <c r="M113" s="8"/>
+      <c r="N113" s="8"/>
+      <c r="O113" s="8"/>
+      <c r="P113" s="8"/>
+      <c r="Q113" s="8"/>
+      <c r="R113" s="8"/>
+      <c r="S113" s="8"/>
+      <c r="T113" s="8"/>
+      <c r="U113" s="8"/>
+    </row>
+    <row r="114" spans="1:21">
+      <c r="A114" s="22" t="s">
         <v>66</v>
       </c>
-      <c r="B113" s="19" t="s">
+      <c r="B114" s="19" t="s">
         <v>149</v>
       </c>
-      <c r="C113" s="19" t="s">
+      <c r="C114" s="19" t="s">
         <v>150</v>
       </c>
-      <c r="D113" s="19"/>
-      <c r="E113" s="19"/>
-      <c r="F113" s="19"/>
-      <c r="G113" s="19"/>
-      <c r="H113" s="19" t="s">
-        <v>249</v>
-      </c>
-      <c r="I113" s="19"/>
-      <c r="J113" s="20"/>
-      <c r="K113" s="19"/>
-      <c r="L113" s="19"/>
-      <c r="M113" s="19"/>
-      <c r="N113" s="19"/>
-      <c r="O113" s="19"/>
-      <c r="P113" s="19"/>
-      <c r="Q113" s="19"/>
-      <c r="R113" s="19"/>
-      <c r="S113" s="19"/>
-      <c r="T113" s="19"/>
-      <c r="U113" s="19"/>
-    </row>
-    <row r="114" spans="1:21">
-      <c r="A114" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="B114" s="8" t="s">
-        <v>151</v>
-      </c>
-      <c r="C114" s="9" t="s">
-        <v>152</v>
-      </c>
-      <c r="D114" s="9"/>
-      <c r="E114" s="8"/>
-      <c r="F114" s="8"/>
-      <c r="G114" s="9"/>
-      <c r="H114" s="8"/>
-      <c r="I114" s="8"/>
-      <c r="J114" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="K114" s="8"/>
-      <c r="L114" s="8"/>
-      <c r="M114" s="8"/>
-      <c r="N114" s="8"/>
-      <c r="O114" s="8"/>
-      <c r="P114" s="8"/>
-      <c r="Q114" s="8"/>
-      <c r="R114" s="8"/>
-      <c r="S114" s="8"/>
-      <c r="T114" s="8"/>
-      <c r="U114" s="8"/>
+      <c r="D114" s="19"/>
+      <c r="E114" s="19"/>
+      <c r="F114" s="19"/>
+      <c r="G114" s="19"/>
+      <c r="H114" s="19" t="s">
+        <v>248</v>
+      </c>
+      <c r="I114" s="19"/>
+      <c r="J114" s="20"/>
+      <c r="K114" s="19"/>
+      <c r="L114" s="19"/>
+      <c r="M114" s="19"/>
+      <c r="N114" s="19"/>
+      <c r="O114" s="19"/>
+      <c r="P114" s="19"/>
+      <c r="Q114" s="19"/>
+      <c r="R114" s="19"/>
+      <c r="S114" s="19"/>
+      <c r="T114" s="19"/>
+      <c r="U114" s="19"/>
     </row>
     <row r="115" spans="1:21">
       <c r="A115" s="21" t="s">
         <v>13</v>
       </c>
       <c r="B115" s="8" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C115" s="9" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="D115" s="9"/>
       <c r="E115" s="8"/>
@@ -5015,10 +4991,10 @@
         <v>13</v>
       </c>
       <c r="B116" s="8" t="s">
-        <v>155</v>
-      </c>
-      <c r="C116" s="27" t="s">
-        <v>264</v>
+        <v>153</v>
+      </c>
+      <c r="C116" s="9" t="s">
+        <v>154</v>
       </c>
       <c r="D116" s="9"/>
       <c r="E116" s="8"/>
@@ -5043,17 +5019,23 @@
     </row>
     <row r="117" spans="1:21">
       <c r="A117" s="21" t="s">
-        <v>79</v>
-      </c>
-      <c r="B117" s="8"/>
-      <c r="C117" s="9"/>
+        <v>13</v>
+      </c>
+      <c r="B117" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="C117" s="27" t="s">
+        <v>263</v>
+      </c>
       <c r="D117" s="9"/>
       <c r="E117" s="8"/>
       <c r="F117" s="8"/>
       <c r="G117" s="9"/>
       <c r="H117" s="8"/>
       <c r="I117" s="8"/>
-      <c r="J117" s="7"/>
+      <c r="J117" s="7" t="s">
+        <v>14</v>
+      </c>
       <c r="K117" s="8"/>
       <c r="L117" s="8"/>
       <c r="M117" s="8"/>
@@ -5067,76 +5049,70 @@
       <c r="U117" s="8"/>
     </row>
     <row r="118" spans="1:21">
-      <c r="A118" s="22" t="s">
+      <c r="A118" s="21" t="s">
+        <v>79</v>
+      </c>
+      <c r="B118" s="8"/>
+      <c r="C118" s="9"/>
+      <c r="D118" s="9"/>
+      <c r="E118" s="8"/>
+      <c r="F118" s="8"/>
+      <c r="G118" s="9"/>
+      <c r="H118" s="8"/>
+      <c r="I118" s="8"/>
+      <c r="J118" s="7"/>
+      <c r="K118" s="8"/>
+      <c r="L118" s="8"/>
+      <c r="M118" s="8"/>
+      <c r="N118" s="8"/>
+      <c r="O118" s="8"/>
+      <c r="P118" s="8"/>
+      <c r="Q118" s="8"/>
+      <c r="R118" s="8"/>
+      <c r="S118" s="8"/>
+      <c r="T118" s="8"/>
+      <c r="U118" s="8"/>
+    </row>
+    <row r="119" spans="1:21">
+      <c r="A119" s="22" t="s">
         <v>66</v>
       </c>
-      <c r="B118" s="19" t="s">
-        <v>282</v>
-      </c>
-      <c r="C118" s="19" t="s">
-        <v>270</v>
-      </c>
-      <c r="D118" s="19"/>
-      <c r="E118" s="19"/>
-      <c r="F118" s="19"/>
-      <c r="G118" s="19"/>
-      <c r="H118" s="19" t="s">
-        <v>249</v>
-      </c>
-      <c r="I118" s="19"/>
-      <c r="J118" s="20"/>
-      <c r="K118" s="19"/>
-      <c r="L118" s="19"/>
-      <c r="M118" s="19"/>
-      <c r="N118" s="19"/>
-      <c r="O118" s="19"/>
-      <c r="P118" s="19"/>
-      <c r="Q118" s="19"/>
-      <c r="R118" s="19"/>
-      <c r="S118" s="19"/>
-      <c r="T118" s="19"/>
-      <c r="U118" s="19"/>
-    </row>
-    <row r="119" spans="1:21">
-      <c r="A119" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="B119" s="8" t="s">
-        <v>156</v>
-      </c>
-      <c r="C119" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="D119" s="9"/>
-      <c r="E119" s="8"/>
-      <c r="F119" s="8"/>
-      <c r="G119" s="9"/>
-      <c r="H119" s="8"/>
-      <c r="I119" s="8"/>
-      <c r="J119" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="K119" s="8"/>
-      <c r="L119" s="8"/>
-      <c r="M119" s="8"/>
-      <c r="N119" s="8"/>
-      <c r="O119" s="8"/>
-      <c r="P119" s="8"/>
-      <c r="Q119" s="8"/>
-      <c r="R119" s="8"/>
-      <c r="S119" s="8"/>
-      <c r="T119" s="8"/>
-      <c r="U119" s="8"/>
+      <c r="B119" s="19" t="s">
+        <v>279</v>
+      </c>
+      <c r="C119" s="19" t="s">
+        <v>267</v>
+      </c>
+      <c r="D119" s="19"/>
+      <c r="E119" s="19"/>
+      <c r="F119" s="19"/>
+      <c r="G119" s="19"/>
+      <c r="H119" s="19" t="s">
+        <v>248</v>
+      </c>
+      <c r="I119" s="19"/>
+      <c r="J119" s="20"/>
+      <c r="K119" s="19"/>
+      <c r="L119" s="19"/>
+      <c r="M119" s="19"/>
+      <c r="N119" s="19"/>
+      <c r="O119" s="19"/>
+      <c r="P119" s="19"/>
+      <c r="Q119" s="19"/>
+      <c r="R119" s="19"/>
+      <c r="S119" s="19"/>
+      <c r="T119" s="19"/>
+      <c r="U119" s="19"/>
     </row>
     <row r="120" spans="1:21">
       <c r="A120" s="21" t="s">
         <v>13</v>
       </c>
       <c r="B120" s="8" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C120" s="9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D120" s="9"/>
       <c r="E120" s="8"/>
@@ -5164,10 +5140,10 @@
         <v>13</v>
       </c>
       <c r="B121" s="8" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C121" s="9" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D121" s="9"/>
       <c r="E121" s="8"/>
@@ -5195,10 +5171,10 @@
         <v>13</v>
       </c>
       <c r="B122" s="8" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C122" s="9" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D122" s="9"/>
       <c r="E122" s="8"/>
@@ -5226,10 +5202,10 @@
         <v>13</v>
       </c>
       <c r="B123" s="8" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C123" s="9" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D123" s="9"/>
       <c r="E123" s="8"/>
@@ -5254,17 +5230,23 @@
     </row>
     <row r="124" spans="1:21">
       <c r="A124" s="21" t="s">
-        <v>79</v>
-      </c>
-      <c r="B124" s="8"/>
-      <c r="C124" s="9"/>
+        <v>13</v>
+      </c>
+      <c r="B124" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="C124" s="9" t="s">
+        <v>73</v>
+      </c>
       <c r="D124" s="9"/>
       <c r="E124" s="8"/>
       <c r="F124" s="8"/>
       <c r="G124" s="9"/>
       <c r="H124" s="8"/>
       <c r="I124" s="8"/>
-      <c r="J124" s="7"/>
+      <c r="J124" s="7" t="s">
+        <v>14</v>
+      </c>
       <c r="K124" s="8"/>
       <c r="L124" s="8"/>
       <c r="M124" s="8"/>
@@ -5278,74 +5260,68 @@
       <c r="U124" s="8"/>
     </row>
     <row r="125" spans="1:21">
-      <c r="A125" s="22" t="s">
+      <c r="A125" s="21" t="s">
+        <v>79</v>
+      </c>
+      <c r="B125" s="8"/>
+      <c r="C125" s="9"/>
+      <c r="D125" s="9"/>
+      <c r="E125" s="8"/>
+      <c r="F125" s="8"/>
+      <c r="G125" s="9"/>
+      <c r="H125" s="8"/>
+      <c r="I125" s="8"/>
+      <c r="J125" s="7"/>
+      <c r="K125" s="8"/>
+      <c r="L125" s="8"/>
+      <c r="M125" s="8"/>
+      <c r="N125" s="8"/>
+      <c r="O125" s="8"/>
+      <c r="P125" s="8"/>
+      <c r="Q125" s="8"/>
+      <c r="R125" s="8"/>
+      <c r="S125" s="8"/>
+      <c r="T125" s="8"/>
+      <c r="U125" s="8"/>
+    </row>
+    <row r="126" spans="1:21">
+      <c r="A126" s="22" t="s">
         <v>66</v>
       </c>
-      <c r="B125" s="19" t="s">
+      <c r="B126" s="19" t="s">
         <v>161</v>
       </c>
-      <c r="C125" s="19" t="s">
+      <c r="C126" s="19" t="s">
         <v>162</v>
       </c>
-      <c r="D125" s="19"/>
-      <c r="E125" s="19"/>
-      <c r="F125" s="19"/>
-      <c r="G125" s="19"/>
-      <c r="H125" s="19"/>
-      <c r="I125" s="19"/>
-      <c r="J125" s="20"/>
-      <c r="K125" s="19"/>
-      <c r="L125" s="19"/>
-      <c r="M125" s="19"/>
-      <c r="N125" s="19"/>
-      <c r="O125" s="19"/>
-      <c r="P125" s="19"/>
-      <c r="Q125" s="19"/>
-      <c r="R125" s="19"/>
-      <c r="S125" s="19"/>
-      <c r="T125" s="19"/>
-      <c r="U125" s="19"/>
-    </row>
-    <row r="126" spans="1:21">
-      <c r="A126" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="B126" s="8" t="s">
-        <v>163</v>
-      </c>
-      <c r="C126" s="9" t="s">
-        <v>164</v>
-      </c>
-      <c r="D126" s="9"/>
-      <c r="E126" s="8"/>
-      <c r="F126" s="8"/>
-      <c r="G126" s="9"/>
-      <c r="H126" s="8"/>
-      <c r="I126" s="8"/>
-      <c r="J126" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="K126" s="8"/>
-      <c r="L126" s="8"/>
-      <c r="M126" s="8"/>
-      <c r="N126" s="8"/>
-      <c r="O126" s="8"/>
-      <c r="P126" s="8"/>
-      <c r="Q126" s="8"/>
-      <c r="R126" s="8"/>
-      <c r="S126" s="8"/>
-      <c r="T126" s="8"/>
-      <c r="U126" s="8"/>
+      <c r="D126" s="19"/>
+      <c r="E126" s="19"/>
+      <c r="F126" s="19"/>
+      <c r="G126" s="19"/>
+      <c r="H126" s="19"/>
+      <c r="I126" s="19"/>
+      <c r="J126" s="20"/>
+      <c r="K126" s="19"/>
+      <c r="L126" s="19"/>
+      <c r="M126" s="19"/>
+      <c r="N126" s="19"/>
+      <c r="O126" s="19"/>
+      <c r="P126" s="19"/>
+      <c r="Q126" s="19"/>
+      <c r="R126" s="19"/>
+      <c r="S126" s="19"/>
+      <c r="T126" s="19"/>
+      <c r="U126" s="19"/>
     </row>
     <row r="127" spans="1:21">
       <c r="A127" s="21" t="s">
         <v>13</v>
       </c>
       <c r="B127" s="8" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C127" s="9" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D127" s="9"/>
       <c r="E127" s="8"/>
@@ -5373,10 +5349,10 @@
         <v>13</v>
       </c>
       <c r="B128" s="8" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C128" s="9" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D128" s="9"/>
       <c r="E128" s="8"/>
@@ -5404,10 +5380,10 @@
         <v>13</v>
       </c>
       <c r="B129" s="8" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C129" s="9" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D129" s="9"/>
       <c r="E129" s="8"/>
@@ -5432,17 +5408,23 @@
     </row>
     <row r="130" spans="1:21">
       <c r="A130" s="21" t="s">
-        <v>79</v>
-      </c>
-      <c r="B130" s="8"/>
-      <c r="C130" s="9"/>
+        <v>13</v>
+      </c>
+      <c r="B130" s="8" t="s">
+        <v>169</v>
+      </c>
+      <c r="C130" s="9" t="s">
+        <v>170</v>
+      </c>
       <c r="D130" s="9"/>
       <c r="E130" s="8"/>
       <c r="F130" s="8"/>
       <c r="G130" s="9"/>
       <c r="H130" s="8"/>
       <c r="I130" s="8"/>
-      <c r="J130" s="7"/>
+      <c r="J130" s="7" t="s">
+        <v>14</v>
+      </c>
       <c r="K130" s="8"/>
       <c r="L130" s="8"/>
       <c r="M130" s="8"/>
@@ -5456,24 +5438,18 @@
       <c r="U130" s="8"/>
     </row>
     <row r="131" spans="1:21">
-      <c r="A131" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="B131" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="C131" s="9" t="s">
-        <v>50</v>
-      </c>
+      <c r="A131" s="21" t="s">
+        <v>79</v>
+      </c>
+      <c r="B131" s="8"/>
+      <c r="C131" s="9"/>
       <c r="D131" s="9"/>
       <c r="E131" s="8"/>
       <c r="F131" s="8"/>
       <c r="G131" s="9"/>
       <c r="H131" s="8"/>
       <c r="I131" s="8"/>
-      <c r="J131" s="7" t="s">
-        <v>51</v>
-      </c>
+      <c r="J131" s="7"/>
       <c r="K131" s="8"/>
       <c r="L131" s="8"/>
       <c r="M131" s="8"/>
@@ -5488,19 +5464,23 @@
     </row>
     <row r="132" spans="1:21">
       <c r="A132" s="8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B132" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C132" s="9"/>
+        <v>49</v>
+      </c>
+      <c r="C132" s="9" t="s">
+        <v>50</v>
+      </c>
       <c r="D132" s="9"/>
       <c r="E132" s="8"/>
       <c r="F132" s="8"/>
       <c r="G132" s="9"/>
       <c r="H132" s="8"/>
       <c r="I132" s="8"/>
-      <c r="J132" s="8"/>
+      <c r="J132" s="7" t="s">
+        <v>51</v>
+      </c>
       <c r="K132" s="8"/>
       <c r="L132" s="8"/>
       <c r="M132" s="8"/>
@@ -5515,10 +5495,10 @@
     </row>
     <row r="133" spans="1:21">
       <c r="A133" s="8" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B133" s="8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C133" s="9"/>
       <c r="D133" s="9"/>
@@ -5539,6 +5519,33 @@
       <c r="S133" s="8"/>
       <c r="T133" s="8"/>
       <c r="U133" s="8"/>
+    </row>
+    <row r="134" spans="1:21">
+      <c r="A134" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B134" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C134" s="9"/>
+      <c r="D134" s="9"/>
+      <c r="E134" s="8"/>
+      <c r="F134" s="8"/>
+      <c r="G134" s="9"/>
+      <c r="H134" s="8"/>
+      <c r="I134" s="8"/>
+      <c r="J134" s="8"/>
+      <c r="K134" s="8"/>
+      <c r="L134" s="8"/>
+      <c r="M134" s="8"/>
+      <c r="N134" s="8"/>
+      <c r="O134" s="8"/>
+      <c r="P134" s="8"/>
+      <c r="Q134" s="8"/>
+      <c r="R134" s="8"/>
+      <c r="S134" s="8"/>
+      <c r="T134" s="8"/>
+      <c r="U134" s="8"/>
     </row>
   </sheetData>
   <phoneticPr fontId="9" type="noConversion"/>
@@ -5569,8 +5576,8 @@
       <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
-        <v>269</v>
+      <c r="D1" s="2" t="s">
+        <v>266</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -5984,10 +5991,10 @@
         <v>81</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C40" s="9" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D40" s="4" t="s">
         <v>201</v>
@@ -5998,10 +6005,10 @@
         <v>81</v>
       </c>
       <c r="B41" s="8" t="s">
+        <v>242</v>
+      </c>
+      <c r="C41" s="9" t="s">
         <v>243</v>
-      </c>
-      <c r="C41" s="9" t="s">
-        <v>244</v>
       </c>
       <c r="D41" s="4" t="s">
         <v>201</v>
@@ -6012,10 +6019,10 @@
         <v>81</v>
       </c>
       <c r="B42" s="8" t="s">
+        <v>244</v>
+      </c>
+      <c r="C42" s="9" t="s">
         <v>245</v>
-      </c>
-      <c r="C42" s="9" t="s">
-        <v>246</v>
       </c>
       <c r="D42" s="4" t="s">
         <v>201</v>
@@ -6084,24 +6091,24 @@
     </row>
     <row r="48" spans="1:4">
       <c r="A48" s="8" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B48" s="8" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C48" s="9" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49" s="8" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B49" s="8" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C49" s="9" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
   </sheetData>
@@ -6137,10 +6144,10 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="3" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="C2" t="s">
         <v>28</v>
